--- a/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
+++ b/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sdk\ast2700\OTP\memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5F94B1-81B8-4B40-8384-4B9580233212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28EE68B-5E3E-4F1E-906C-B9764394DDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -3623,7 +3623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4077,29 +4077,23 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4504,13 +4498,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="125" t="s">
@@ -7440,10 +7434,10 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="152" t="s">
+      <c r="A61" s="151" t="s">
         <v>356</v>
       </c>
-      <c r="B61" s="153" t="s">
+      <c r="B61" s="152" t="s">
         <v>26</v>
       </c>
       <c r="C61" s="102" t="s">
@@ -7463,10 +7457,10 @@
       <c r="G61" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="H61" s="157" t="s">
+      <c r="H61" s="154" t="s">
         <v>684</v>
       </c>
-      <c r="I61" s="158" t="s">
+      <c r="I61" s="155" t="s">
         <v>392</v>
       </c>
     </row>
@@ -7477,7 +7471,7 @@
       <c r="B62" s="29" t="s">
         <v>698</v>
       </c>
-      <c r="C62" s="154">
+      <c r="C62" s="64">
         <v>7</v>
       </c>
       <c r="D62" s="16">
@@ -7508,7 +7502,7 @@
       <c r="B63" s="29" t="s">
         <v>699</v>
       </c>
-      <c r="C63" s="154">
+      <c r="C63" s="64">
         <v>6</v>
       </c>
       <c r="D63" s="16">
@@ -7539,7 +7533,7 @@
       <c r="B64" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="C64" s="154">
+      <c r="C64" s="64">
         <v>5</v>
       </c>
       <c r="D64" s="16">
@@ -7570,7 +7564,7 @@
       <c r="B65" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="C65" s="154">
+      <c r="C65" s="64">
         <v>4</v>
       </c>
       <c r="D65" s="16">
@@ -7601,7 +7595,7 @@
       <c r="B66" s="29" t="s">
         <v>702</v>
       </c>
-      <c r="C66" s="154">
+      <c r="C66" s="64">
         <v>3</v>
       </c>
       <c r="D66" s="16">
@@ -7632,7 +7626,7 @@
       <c r="B67" s="29" t="s">
         <v>703</v>
       </c>
-      <c r="C67" s="154">
+      <c r="C67" s="64">
         <v>2</v>
       </c>
       <c r="D67" s="16">
@@ -7663,7 +7657,7 @@
       <c r="B68" s="29" t="s">
         <v>704</v>
       </c>
-      <c r="C68" s="154">
+      <c r="C68" s="64">
         <v>1</v>
       </c>
       <c r="D68" s="16">
@@ -7691,10 +7685,10 @@
       <c r="A69" s="122" t="s">
         <v>356</v>
       </c>
-      <c r="B69" s="155" t="s">
+      <c r="B69" s="153" t="s">
         <v>705</v>
       </c>
-      <c r="C69" s="156">
+      <c r="C69" s="95">
         <v>0</v>
       </c>
       <c r="D69" s="66">
@@ -14773,7 +14767,7 @@
         <v>587</v>
       </c>
       <c r="C39" s="96" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D39" s="59">
         <v>256</v>
@@ -14802,7 +14796,7 @@
         <v>588</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D40" s="59">
         <v>256</v>
@@ -14831,7 +14825,7 @@
         <v>589</v>
       </c>
       <c r="C41" s="96" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D41" s="59">
         <v>256</v>
@@ -14860,7 +14854,7 @@
         <v>590</v>
       </c>
       <c r="C42" s="96" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D42" s="59">
         <v>256</v>
@@ -15301,6 +15295,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB031FF8E1109D43B2BDF0F43F684A4E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b896ebdbfa452e7a07541eac816e2062">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94916c3f-a887-466e-9071-419f2f5fc067" xmlns:ns3="0358a91d-8923-4300-9035-92feb74d70aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="556acc82b7336cf142ff4903a3ab7ecb" ns2:_="" ns3:_="">
     <xsd:import namespace="94916c3f-a887-466e-9071-419f2f5fc067"/>
@@ -15555,49 +15577,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
-    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15620,9 +15603,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
+    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
+++ b/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sdk\ast2700\OTP\memory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28EE68B-5E3E-4F1E-906C-B9764394DDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A973C1CC-7133-4C88-AF1F-3DA5E22E17E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <definedName name="otp_macro_base">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">OTPCAL!$A$1:$H$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">OTPPUF!$A$1:$H$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">OTPRBP!$A$1:$H$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">OTPRBP!$A$1:$H$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">OTPROM!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="719">
   <si>
     <t>High Level overview of OTP memory layout</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Reserved</t>
-  </si>
-  <si>
-    <t>Caliptra Owner public key hash retire</t>
   </si>
   <si>
     <t>Secure Boot - key retire</t>
@@ -258,10 +255,6 @@
   <si>
     <t>enable_secure_boot</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>retire_mechanism_option</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>wr_protect_otp_strap</t>
@@ -407,11 +400,6 @@
   </si>
   <si>
     <t>otp_patch_vld 1</t>
-  </si>
-  <si>
-    <t>Enable otp patch 1
-0: otp rom patch 1 is invalid
-1: otp rom patch 1 is valid</t>
   </si>
   <si>
     <t>OTP Patch Size 1</t>
@@ -2574,25 +2562,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Caliptra Owner public key hash retire bits
-Caliptra owner pk hash is used of populate inof Caliptra fuse for Caliptra owner keys verification. AST27x0 supports up of 16 Caliptra owner pk hash and supports pk hash retirement feature.
-Check Caliptra spec for more details. (https://github.com/chipsalliance/Caliptra/blob/main/doc/caliptra_1x/Caliptra.md)
-Effect: Secure boot is enabled
-Policy: OTPCFG0[8]</t>
-  </si>
-  <si>
-    <t>SoC Manifest hardware security version number
-SoC Manifest SVN must be equal of or greater than hardware SVN for rollback prevention otherwise the secure boot check is failure. It's implemented a hardware write protection of prevent malicious attack, the new SVN (of-be prog) must be smaller than or equal of current SVN.
-Effect: Secure boot is enabled
-Boot up Policy: SoC Manifest SVN &gt;= HW SoC Manifest SVN</t>
-  </si>
-  <si>
-    <t>Disable OTP Memory Facofry Test Mode
-0: enable
-1: disable
-of prevent security issue of OTP memory. Disabled BIST mode is recommended.</t>
-  </si>
-  <si>
     <t>Enable Secure Boot
 0:disable
 1:enable
@@ -2612,341 +2581,392 @@
 1: eMMC software reset enable. Always do software reset</t>
   </si>
   <si>
+    <t>OTP Patch 1 code size (unit: word)
+The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
+  </si>
+  <si>
+    <t>OTP Patch 2 code size (unit: word)
+The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART5 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART3 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART2 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART1 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART0 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART10 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART9 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART8 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART7 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART6 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable UART of put all boot message and wait the completetion</t>
+  </si>
+  <si>
+    <t>Enable Mode-0 hub of support 23 ports</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART15 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART12 Tx Discard</t>
+  </si>
+  <si>
+    <t>Enable of turn off UART11 Tx Discard</t>
+  </si>
+  <si>
+    <t>OTP Patch 3 code size (unit: word)
+The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
+  </si>
+  <si>
+    <t>OTP Patch 4 code size (unit: word)
+The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
+  </si>
+  <si>
+    <t>OTP Patch 5 code size (unit: word)
+The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
+  </si>
+  <si>
+    <t>AST27x0 has two die, one is IO-die, the other is CPU-die.
+In case of there has some errors between die of die connection, this field is a backup solution of boot from CPU-die.</t>
+  </si>
+  <si>
+    <t>VGA linear memory size
+SW-ROM write of DRAMC100[0]</t>
+  </si>
+  <si>
+    <t>Enable secure boot for production, but allow it of be disabled for debugging.</t>
+  </si>
+  <si>
+    <t>WDT full chip reset function can reset full chip. This field can disable full chip, WDT0C[6:5] = 2b'01, reset function permanently of prevent malicious attack.
+Note: This bit must be set ofgether with OTPSTRAP_EXT[25].</t>
+  </si>
+  <si>
+    <t>This bit is used of disable Caliptra JTAG permanently.</t>
+  </si>
+  <si>
+    <t>Boot ROM has an option of enable interrupts for backup solution.</t>
+  </si>
+  <si>
+    <t>Disable BootMCU ROM &amp; jump of FMC
+0: enable 1: disable
+(wlock)</t>
+  </si>
+  <si>
+    <t>This bit must be kept cleared (0) and write-locked after the MP stage, as it is used of bypass the BootMCU ROM code.
+Enabling this bit may result in unexpected or unsafe boot behavior and is therefore not recommended for normal operation.</t>
+  </si>
+  <si>
+    <t>When booting from eMMC or UFS is selected via an external pin strap, this bit is used of select the BMC boot source between eMMC and UFS.</t>
+  </si>
+  <si>
+    <t>Allow BROM of wait SPI flash ready bit
+0: disable 1: enable</t>
+  </si>
+  <si>
+    <t>When this bit is enabled, the BMC checks the ready/busy status of the FWSPI flash before reading the boot image, of handle cases where a warm reset occurs during erase or program operations. The BMC determines the flash status by issuing the 05h (Read Status Register) command and polling the WIP (Write In Progress) bit. The BMC will wait until the flash becomes ready, with a maximum wait time of 16 seconds, before accessing the boot image.</t>
+  </si>
+  <si>
+    <t>Use 4-byte command of read flash
+0: disable 1: enable</t>
+  </si>
+  <si>
+    <t>SPI_Flash_4_Byte_Mode is used of prevent address mode mismatch between the BMC and the SPI flash.
+After a full chip reset or when the SRST# pin is not connected of the SPI flash, the BMC always resets of 3-byte address mode, while the SPI flash may remain in 4-byte address mode. This mismatch can cause SPI access failures and lead of boot-up issues. When this OTP bit is enabled, the BMC will use dedicated 4-byte address SPI instructions, 13h, of read the flash. These instructions can correctly read flash data regardless of the current address mode of the flash, ensuring reliable boot behavior.</t>
+  </si>
+  <si>
+    <t>When recovery mode is enabled, the default recovery interface is UART. This field allows users of select different recovery interface.</t>
+  </si>
+  <si>
+    <t>This is an option if cusofmer don't need Caliptra in AST27x0.</t>
+  </si>
+  <si>
+    <t>Duplicate of 422</t>
+  </si>
+  <si>
+    <t>Duplicate of 423</t>
+  </si>
+  <si>
+    <t>The optional bit is reserved for an external UFS oscillaofr as an alternative solution. This oscillaofr is a 1.2 V, 26 MHz source that provides input of both the MPHY reference clock and the UFS device simultaneously. Under normal conditions, we use an internal clock source for the MPHY. However, in case high-temperature conditions cause the PLL of become unstable, we have several fallback options for the MPHY reference clock.</t>
+  </si>
+  <si>
+    <t>If users still want of debug in Normal world, but Secure world is not allowed for security. This is an option of disable it.</t>
+  </si>
+  <si>
+    <t>WDT full chip reset function can reset full chip. This field can disable full chip, WDT0C[6:5] = 2b'01, reset function permanently of prevent malicious attack.</t>
+  </si>
+  <si>
+    <t>Uart Debug timeout selection
+default: unlimited
+need of sync CPU-die reg</t>
+  </si>
+  <si>
+    <t>Note: This bit must be set ofgether with OTPSTRAP[18].</t>
+  </si>
+  <si>
+    <t>boot sofrage ABR enable
+0: disable 1: enable</t>
+  </si>
+  <si>
+    <t>This bit is used of enabled ABR machenism.</t>
+  </si>
+  <si>
+    <t>When this bit is set and a secure-related error is detected, the image previously loaded inof SRAM will be cleared, preventing the execution of potentially invalid or compromised code.
+Note: Enabling this bit may affect the problem debug process, as the original failure context or error location in SRAM may be cleared and no longer observable.</t>
+  </si>
+  <si>
+    <t>This is the source of Caliptra security state. It populates inof Caliptra fuse map. See Caliptra spec for more details. (https://github.com/chipsalliance/Caliptra/blob/main/doc/caliptra_1x/Caliptra.md#caliptra-security-states)</t>
+  </si>
+  <si>
+    <t>When single-flash ABR mode is enabled, this field must be set of specify the FWSPI flash size. When a single-flash ABR event is triggered, the BMC will fetch the boot image from an offset equal of half of the flash size, based on the value configured in this field.</t>
+  </si>
+  <si>
+    <t>When this bit is enabled, system can force BMC of boot from alternate flash part by controlling an external pin signal, pull high.</t>
+  </si>
+  <si>
+    <t>After power-on or reset, the FWSPI clock frequency defaults of 12.5 MHz for booting purposes. This field allows system developers of configure the FWSPI clock frequency used during the boot stage only and does not affect the FWSPI clock after the system has booted.</t>
+  </si>
+  <si>
+    <t>When this bit is enabled, the BMC will verify the existence of the FWSPI flash before attempting of read the boot image. The BMC checks for flash presence by reading the SFDP (Serial Flash Discoverable Parameters) magic number, which is a standard identifier supported by common SPI NOR flash devices. If the flash device is not detected, the BMC will wait for up of 7 seconds before proceeding, allowing time for the flash of become available and avoiding premature boot failures.</t>
+  </si>
+  <si>
+    <t>When ABR is enabled, by default on AST2700, if the BMC fails of boot from part A, it will attempt of boot from part B after WDTA timeout. If part B also fails of boot, the BMC will enter recovery mode after another WDTA timeout. The default boot sequence is: "Part A → Part B → Recovery". When ABR_RECOVERY_DIS is set, the recovery behavior is disabled, and the boot sequence becomes: "Part A → Part B → Part A → Part B → …"</t>
+  </si>
+  <si>
+    <t>This bit is not recommended of be enabled on AST2700 A1 and A2 and is provided only as a backup solution for the dual-flash ABR mechanism. By default, when the dual-flash ABR mechanism is triggered, the BMC hardware will auofmatically swap the address space of FWSPI CS0 and CS1 of select the backup flash. When this bit is set, the hardware will not perform the CS0/CS1 address space swap, and the dual-flash ABR mechanism relies on software handling instead.</t>
+  </si>
+  <si>
+    <t>This bit is used of select the ABR operating mode.
+- When dual-flash ABR mode is selected, this bit must be cleared.
+- When single-flash ABR mode is selected, this bit must be set.</t>
+  </si>
+  <si>
+    <t>Reserved for cusofmers (OEM/ODM)</t>
+  </si>
+  <si>
+    <t>Header of elaborate the key type, offset, etc.</t>
+  </si>
+  <si>
+    <t>Secure vault key is dedicated of encryption/decryption</t>
+  </si>
+  <si>
+    <t>Caliptra fuse: FIELD ENTROPY
+Owner secret of hedge against UDS disclosure in the supply chain</t>
+  </si>
+  <si>
+    <t>Reserved of cusofmers</t>
+  </si>
+  <si>
+    <t>Caliptra OBF Key (HW auof load)</t>
+  </si>
+  <si>
+    <t>Reserved of SCU1_7E0</t>
+  </si>
+  <si>
+    <t>Reserved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40A</t>
+  </si>
+  <si>
+    <t>DBG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reference to datasheet SCU1_0C8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reserved</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reference to datasheet SCU0_0C8</t>
+  </si>
+  <si>
+    <t>Reference to datasheet SCU0_0C8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OTPCFG9/SCU1_890</t>
+  </si>
+  <si>
+    <t>OTPCFG9/SCU1_890</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable auto load debug control SCU0_0C8/SCU1_0C8 setting
+0:disable
+1:enable of auto load SCU0_0C8/SCU1_0C8 value
+After SCU0_0C8 is loaded, the write protection SCU0_E04[18] will be set.
+After SCU1_0C8 is loaded, the write protection SCU1_B04[18] will be set.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>en_auto_load SCU debug control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCU0_DIS_RSA_PRIV_KEY_READ</t>
+  </si>
+  <si>
+    <t>SCU0_DIS_XDMA_VGA</t>
+  </si>
+  <si>
+    <t>SCU0_DIS_L2A</t>
+  </si>
+  <si>
+    <t>SCU0_DIS_PCIE_TRACE_BUF</t>
+  </si>
+  <si>
+    <t>SCU0_DIS_XDMA</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_WDT_RSTFULL</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_UART_DBG</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_LPC1_BRIDGE_2</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_LPC0_BRIDGE_2</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_LPC1_BRIDGE_1</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_LPC0_BRIDGE_1</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_ESPI1_AHB</t>
+  </si>
+  <si>
+    <t>SCU1_DIS_ESPI0_AHB</t>
+  </si>
+  <si>
+    <t>SCU0_DIS_UART_DBG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCU0_DIS_WDT_RSTFULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>en_auto_load_usr0</t>
+  </si>
+  <si>
+    <t>Enable auto load OTP user0 ctrl setting of OTP register.
+Once it's enabled, r/w protection, offset, and size of OTP user0 value below would be loaded inof OTP control registers as a hardware default value.</t>
+  </si>
+  <si>
+    <t>en_auto_load_secure0</t>
+  </si>
+  <si>
+    <t>Enable auto load OTP secure0 ctrl setting of OTP register.
+Once it's enabled, r/w protection, offset, and size of OTP secure0 value below would be loaded inof OTP controller registers as a hardware default value.</t>
+  </si>
+  <si>
+    <t>en_auto_load_cptra0</t>
+  </si>
+  <si>
+    <t>Enable auto load OTP cptra0 ctrl setting of OTP register.
+Once it's enabled, r/w protection, offset, and size of OTP cptra0 value below would be loaded inof OTP controller registers as a hardware default value.</t>
+  </si>
+  <si>
+    <t>udbg_to_sel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caliptra Owner public key hash retire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable OTP Memory Facofry Test Mode
+0: enable
+1: disable
+of prevent security issue of OTP memory. Disabled BIST mode is recommended.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Disable ROM Patch code
 0: If the OTPCFG2[0] is set, the Boot ROM would
 execute the OTP patch codes which has been programmed inof
 OTPROM region.
 1: The Boot ROM would ignore pre ROM patch.
 The ROM patch is the early stage of the boot ROM boot process.</t>
-  </si>
-  <si>
-    <t>OTP Patch 1 code size (unit: word)
-The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
-  </si>
-  <si>
-    <t>OTP Patch 2 code size (unit: word)
-The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART5 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART3 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART2 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART1 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART0 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART10 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART9 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART8 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART7 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART6 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable UART of put all boot message and wait the completetion</t>
-  </si>
-  <si>
-    <t>Enable Mode-0 hub of support 23 ports</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART15 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART12 Tx Discard</t>
-  </si>
-  <si>
-    <t>Enable of turn off UART11 Tx Discard</t>
-  </si>
-  <si>
-    <t>OTP Patch 3 code size (unit: word)
-The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
-  </si>
-  <si>
-    <t>OTP Patch 4 code size (unit: word)
-The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
-  </si>
-  <si>
-    <t>OTP Patch 5 code size (unit: word)
-The Boot ROM can execute OTP patch codes in OTPROM region. The OTP patch code size is limited of 16Kbit.</t>
-  </si>
-  <si>
-    <t>AST27x0 has two die, one is IO-die, the other is CPU-die.
-In case of there has some errors between die of die connection, this field is a backup solution of boot from CPU-die.</t>
-  </si>
-  <si>
-    <t>VGA linear memory size
-SW-ROM write of DRAMC100[0]</t>
-  </si>
-  <si>
-    <t>Enable secure boot for production, but allow it of be disabled for debugging.</t>
-  </si>
-  <si>
-    <t>WDT full chip reset function can reset full chip. This field can disable full chip, WDT0C[6:5] = 2b'01, reset function permanently of prevent malicious attack.
-Note: This bit must be set ofgether with OTPSTRAP_EXT[25].</t>
-  </si>
-  <si>
-    <t>This bit is used of disable Caliptra JTAG permanently.</t>
-  </si>
-  <si>
-    <t>Boot ROM has an option of enable interrupts for backup solution.</t>
-  </si>
-  <si>
-    <t>Disable BootMCU ROM &amp; jump of FMC
-0: enable 1: disable
-(wlock)</t>
-  </si>
-  <si>
-    <t>This bit must be kept cleared (0) and write-locked after the MP stage, as it is used of bypass the BootMCU ROM code.
-Enabling this bit may result in unexpected or unsafe boot behavior and is therefore not recommended for normal operation.</t>
-  </si>
-  <si>
-    <t>When booting from eMMC or UFS is selected via an external pin strap, this bit is used of select the BMC boot source between eMMC and UFS.</t>
-  </si>
-  <si>
-    <t>Allow BROM of wait SPI flash ready bit
-0: disable 1: enable</t>
-  </si>
-  <si>
-    <t>When this bit is enabled, the BMC checks the ready/busy status of the FWSPI flash before reading the boot image, of handle cases where a warm reset occurs during erase or program operations. The BMC determines the flash status by issuing the 05h (Read Status Register) command and polling the WIP (Write In Progress) bit. The BMC will wait until the flash becomes ready, with a maximum wait time of 16 seconds, before accessing the boot image.</t>
-  </si>
-  <si>
-    <t>Use 4-byte command of read flash
-0: disable 1: enable</t>
-  </si>
-  <si>
-    <t>SPI_Flash_4_Byte_Mode is used of prevent address mode mismatch between the BMC and the SPI flash.
-After a full chip reset or when the SRST# pin is not connected of the SPI flash, the BMC always resets of 3-byte address mode, while the SPI flash may remain in 4-byte address mode. This mismatch can cause SPI access failures and lead of boot-up issues. When this OTP bit is enabled, the BMC will use dedicated 4-byte address SPI instructions, 13h, of read the flash. These instructions can correctly read flash data regardless of the current address mode of the flash, ensuring reliable boot behavior.</t>
-  </si>
-  <si>
-    <t>When recovery mode is enabled, the default recovery interface is UART. This field allows users of select different recovery interface.</t>
-  </si>
-  <si>
-    <t>This is an option if cusofmer don't need Caliptra in AST27x0.</t>
-  </si>
-  <si>
-    <t>Duplicate of 422</t>
-  </si>
-  <si>
-    <t>Duplicate of 423</t>
-  </si>
-  <si>
-    <t>The optional bit is reserved for an external UFS oscillaofr as an alternative solution. This oscillaofr is a 1.2 V, 26 MHz source that provides input of both the MPHY reference clock and the UFS device simultaneously. Under normal conditions, we use an internal clock source for the MPHY. However, in case high-temperature conditions cause the PLL of become unstable, we have several fallback options for the MPHY reference clock.</t>
-  </si>
-  <si>
-    <t>If users still want of debug in Normal world, but Secure world is not allowed for security. This is an option of disable it.</t>
-  </si>
-  <si>
-    <t>WDT full chip reset function can reset full chip. This field can disable full chip, WDT0C[6:5] = 2b'01, reset function permanently of prevent malicious attack.</t>
-  </si>
-  <si>
-    <t>Uart Debug timeout selection
-default: unlimited
-need of sync CPU-die reg</t>
-  </si>
-  <si>
-    <t>Note: This bit must be set ofgether with OTPSTRAP[18].</t>
-  </si>
-  <si>
-    <t>boot sofrage ABR enable
-0: disable 1: enable</t>
-  </si>
-  <si>
-    <t>This bit is used of enabled ABR machenism.</t>
-  </si>
-  <si>
-    <t>When this bit is set and a secure-related error is detected, the image previously loaded inof SRAM will be cleared, preventing the execution of potentially invalid or compromised code.
-Note: Enabling this bit may affect the problem debug process, as the original failure context or error location in SRAM may be cleared and no longer observable.</t>
-  </si>
-  <si>
-    <t>This is the source of Caliptra security state. It populates inof Caliptra fuse map. See Caliptra spec for more details. (https://github.com/chipsalliance/Caliptra/blob/main/doc/caliptra_1x/Caliptra.md#caliptra-security-states)</t>
-  </si>
-  <si>
-    <t>When single-flash ABR mode is enabled, this field must be set of specify the FWSPI flash size. When a single-flash ABR event is triggered, the BMC will fetch the boot image from an offset equal of half of the flash size, based on the value configured in this field.</t>
-  </si>
-  <si>
-    <t>When this bit is enabled, system can force BMC of boot from alternate flash part by controlling an external pin signal, pull high.</t>
-  </si>
-  <si>
-    <t>After power-on or reset, the FWSPI clock frequency defaults of 12.5 MHz for booting purposes. This field allows system developers of configure the FWSPI clock frequency used during the boot stage only and does not affect the FWSPI clock after the system has booted.</t>
-  </si>
-  <si>
-    <t>When this bit is enabled, the BMC will verify the existence of the FWSPI flash before attempting of read the boot image. The BMC checks for flash presence by reading the SFDP (Serial Flash Discoverable Parameters) magic number, which is a standard identifier supported by common SPI NOR flash devices. If the flash device is not detected, the BMC will wait for up of 7 seconds before proceeding, allowing time for the flash of become available and avoiding premature boot failures.</t>
-  </si>
-  <si>
-    <t>When ABR is enabled, by default on AST2700, if the BMC fails of boot from part A, it will attempt of boot from part B after WDTA timeout. If part B also fails of boot, the BMC will enter recovery mode after another WDTA timeout. The default boot sequence is: "Part A → Part B → Recovery". When ABR_RECOVERY_DIS is set, the recovery behavior is disabled, and the boot sequence becomes: "Part A → Part B → Part A → Part B → …"</t>
-  </si>
-  <si>
-    <t>This bit is not recommended of be enabled on AST2700 A1 and A2 and is provided only as a backup solution for the dual-flash ABR mechanism. By default, when the dual-flash ABR mechanism is triggered, the BMC hardware will auofmatically swap the address space of FWSPI CS0 and CS1 of select the backup flash. When this bit is set, the hardware will not perform the CS0/CS1 address space swap, and the dual-flash ABR mechanism relies on software handling instead.</t>
-  </si>
-  <si>
-    <t>This bit is used of select the ABR operating mode.
-- When dual-flash ABR mode is selected, this bit must be cleared.
-- When single-flash ABR mode is selected, this bit must be set.</t>
-  </si>
-  <si>
-    <t>Reserved for cusofmers (OEM/ODM)</t>
-  </si>
-  <si>
-    <t>Header of elaborate the key type, offset, etc.</t>
-  </si>
-  <si>
-    <t>Secure vault key is dedicated of encryption/decryption</t>
-  </si>
-  <si>
-    <t>Caliptra fuse: FIELD ENTROPY
-Owner secret of hedge against UDS disclosure in the supply chain</t>
-  </si>
-  <si>
-    <t>of-be-signed (TBS) payload.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable otp patch 1
+0: otp rom patch 1 is invalid
+1: otp rom patch 1 is valid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to-be-signed (TBS) payload.
 The TBS is the certificate template already patched with the IDevID public key, Subject Key Identifier, serial number, and any extensions that are unique of the device that the vendor may have included.
 Maximum size is 916 bytes according of mailbox command</t>
-  </si>
-  <si>
-    <t>Reserved of cusofmers</t>
-  </si>
-  <si>
-    <t>Caliptra OBF Key (HW auof load)</t>
-  </si>
-  <si>
-    <t>Reserved of SCU1_7E0</t>
-  </si>
-  <si>
-    <t>Reserved</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key retirement mechanism option enable
-0: can only retire itself key #id
-1: can retire others key #id except itself
-There are some key retire bits in OTPRBP region (ex: OTPRBP0/1/3) used of be programmed if the keys need of be retired. This option chooses the retire mechanism policy for different use cases.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40A</t>
-  </si>
-  <si>
-    <t>DBG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reference to datasheet SCU1_0C8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reserved</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reference to datasheet SCU0_0C8</t>
-  </si>
-  <si>
-    <t>Reference to datasheet SCU0_0C8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OTPCFG9/SCU1_890</t>
-  </si>
-  <si>
-    <t>OTPCFG9/SCU1_890</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enable auto load debug control SCU0_0C8/SCU1_0C8 setting
-0:disable
-1:enable of auto load SCU0_0C8/SCU1_0C8 value
-After SCU0_0C8 is loaded, the write protection SCU0_E04[18] will be set.
-After SCU1_0C8 is loaded, the write protection SCU1_B04[18] will be set.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>en_auto_load SCU debug control</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCU0_DIS_RSA_PRIV_KEY_READ</t>
-  </si>
-  <si>
-    <t>SCU0_DIS_XDMA_VGA</t>
-  </si>
-  <si>
-    <t>SCU0_DIS_L2A</t>
-  </si>
-  <si>
-    <t>SCU0_DIS_PCIE_TRACE_BUF</t>
-  </si>
-  <si>
-    <t>SCU0_DIS_XDMA</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_WDT_RSTFULL</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_UART_DBG</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_LPC1_BRIDGE_2</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_LPC0_BRIDGE_2</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_LPC1_BRIDGE_1</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_LPC0_BRIDGE_1</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_ESPI1_AHB</t>
-  </si>
-  <si>
-    <t>SCU1_DIS_ESPI0_AHB</t>
-  </si>
-  <si>
-    <t>SCU0_DIS_UART_DBG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCU0_DIS_WDT_RSTFULL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>en_auto_load_usr0</t>
-  </si>
-  <si>
-    <t>Enable auto load OTP user0 ctrl setting of OTP register.
-Once it's enabled, r/w protection, offset, and size of OTP user0 value below would be loaded inof OTP control registers as a hardware default value.</t>
-  </si>
-  <si>
-    <t>en_auto_load_secure0</t>
-  </si>
-  <si>
-    <t>Enable auto load OTP secure0 ctrl setting of OTP register.
-Once it's enabled, r/w protection, offset, and size of OTP secure0 value below would be loaded inof OTP controller registers as a hardware default value.</t>
-  </si>
-  <si>
-    <t>en_auto_load_cptra0</t>
-  </si>
-  <si>
-    <t>Enable auto load OTP cptra0 ctrl setting of OTP register.
-Once it's enabled, r/w protection, offset, and size of OTP cptra0 value below would be loaded inof OTP controller registers as a hardware default value.</t>
-  </si>
-  <si>
-    <t>udbg_to_sel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoC FMC Hardware SVN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dis_fmc_arb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dis_cptra_owner_key_retry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable Caliptra owner keyhash retry mechanism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable SoC FMC Anti-rollback feature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caliptra Owner public key hash retire
+Caliptra owner pk hash is used of populate inof Caliptra fuse for Caliptra owner keys verification. AST27x0 supports up of 16 Caliptra owner pk hash and supports pk hash retirement feature.
+Check Caliptra spec for more details. (https://github.com/chipsalliance/Caliptra/blob/main/doc/caliptra_1x/Caliptra.md)
+Effect: Secure boot is enabled
+Policy: OTPCFG0[8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoC Manifest hardware SVN
+SoC Manifest SVN must be equal of or greater than hardware SVN for rollback prevention otherwise the secure boot check is failure. It's implemented a hardware write protection of prevent malicious attack, the new SVN (of-be prog) must be smaller than or equal of current SVN.
+Effect: Secure boot is enabled
+Boot up Policy: SoC Manifest SVN &gt;= HW SoC Manifest SVN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoC FMC hardware SVN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4511,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4643,7 +4663,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="128" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B9" s="120" t="str">
         <f t="shared" si="5"/>
@@ -4829,22 +4849,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -4855,13 +4875,13 @@
     </row>
     <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C2" s="124" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D2" s="18">
         <v>512</v>
@@ -4875,7 +4895,7 @@
         <v>32</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="H2" s="18"/>
     </row>
@@ -4885,10 +4905,10 @@
         <v>1FA0</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C3" s="124" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D3" s="18">
         <v>256</v>
@@ -4902,10 +4922,10 @@
         <v>16</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -4914,10 +4934,10 @@
         <v>1FB0</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D4" s="18">
         <v>384</v>
@@ -4931,10 +4951,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -4943,10 +4963,10 @@
         <v>1FC8</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C5" s="124" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D5" s="18">
         <v>256</v>
@@ -4960,10 +4980,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4972,10 +4992,10 @@
         <v>1FD8</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C6" s="124" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D6" s="18">
         <v>256</v>
@@ -4989,10 +5009,10 @@
         <v>16</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5001,10 +5021,10 @@
         <v>1FE8</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C7" s="124" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D7" s="18">
         <v>384</v>
@@ -5028,7 +5048,7 @@
         <v>2000</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="58">
@@ -5092,22 +5112,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5124,7 +5144,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D2" s="8">
         <v>15872</v>
@@ -5138,7 +5158,7 @@
         <v>992</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -5197,7 +5217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C5886-7CD8-42E0-9230-019EC22A238E}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.625" style="3" customWidth="1"/>
@@ -5214,22 +5234,22 @@
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5255,17 +5275,17 @@
         <v>25</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D2" s="8">
         <v>16</v>
       </c>
       <c r="E2" s="8">
-        <f t="shared" ref="E2:E11" si="0">QUOTIENT(D2+7,8)</f>
+        <f t="shared" ref="E2:E12" si="0">QUOTIENT(D2+7,8)</f>
         <v>2</v>
       </c>
       <c r="F2" s="8">
-        <f t="shared" ref="F2:F11" si="1">QUOTIENT(E2+1,2)</f>
+        <f t="shared" ref="F2:F12" si="1">QUOTIENT(E2+1,2)</f>
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
@@ -5275,14 +5295,14 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="146" t="str">
-        <f t="shared" ref="A3:A12" si="2">DEC2HEX(HEX2DEC(A2)+F2)</f>
+        <f t="shared" ref="A3:A13" si="2">DEC2HEX(HEX2DEC(A2)+F2)</f>
         <v>3E1</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D3" s="16">
         <v>16</v>
@@ -5309,7 +5329,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D4" s="16">
         <v>16</v>
@@ -5333,10 +5353,10 @@
         <v>3E3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>27</v>
+        <v>706</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D5" s="16">
         <v>16</v>
@@ -5350,10 +5370,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>613</v>
+        <v>716</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="110.25" x14ac:dyDescent="0.25">
@@ -5362,10 +5382,10 @@
         <v>3E4</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D6" s="16">
         <v>64</v>
@@ -5379,10 +5399,10 @@
         <v>4</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>614</v>
+        <v>717</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="47.25" x14ac:dyDescent="0.25">
@@ -5391,10 +5411,10 @@
         <v>3E8</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D7" s="16">
         <v>32</v>
@@ -5408,10 +5428,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="47.25" x14ac:dyDescent="0.25">
@@ -5420,10 +5440,10 @@
         <v>3EA</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D8" s="16">
         <v>128</v>
@@ -5437,39 +5457,39 @@
         <v>8</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="146" t="str">
-        <f t="shared" ref="A9:A11" si="5">DEC2HEX(HEX2DEC(A8)+F8)</f>
+        <f t="shared" ref="A9:A12" si="5">DEC2HEX(HEX2DEC(A8)+F8)</f>
         <v>3F2</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D9" s="16">
         <v>4</v>
       </c>
       <c r="E9" s="18">
-        <f t="shared" ref="E9:E10" si="6">QUOTIENT(D9+7,8)</f>
+        <f t="shared" ref="E9:E11" si="6">QUOTIENT(D9+7,8)</f>
         <v>1</v>
       </c>
       <c r="F9" s="18">
-        <f t="shared" ref="F9:F10" si="7">QUOTIENT(E9+1,2)</f>
+        <f t="shared" ref="F9:F11" si="7">QUOTIENT(E9+1,2)</f>
         <v>1</v>
       </c>
       <c r="G9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="23" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5478,10 +5498,10 @@
         <v>3F3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D10" s="16">
         <v>32</v>
@@ -5495,10 +5515,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -5506,77 +5526,106 @@
         <f t="shared" si="5"/>
         <v>3F5</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="18" t="s">
+        <v>711</v>
+      </c>
+      <c r="C11" s="96" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="16">
+        <v>128</v>
+      </c>
+      <c r="E11" s="18">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="149" t="str">
+        <f t="shared" si="5"/>
+        <v>3FD</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="D11" s="24">
+      <c r="C12" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" s="24">
         <v>176</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E12" s="24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F12" s="24">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G12" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H12" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="str">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="B12" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="12">
-        <f>SUM(D2:D11)</f>
-        <v>500</v>
-      </c>
-      <c r="E12" s="12">
-        <f>SUM(E2:E11)</f>
-        <v>63</v>
-      </c>
-      <c r="F12" s="12">
-        <f>SUM(F2:F11)</f>
-        <v>32</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
-        <f>DEC2HEX(F13)</f>
-        <v>20</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="61"/>
+      <c r="D13" s="12">
+        <f>SUM(D2:D12)</f>
+        <v>628</v>
+      </c>
+      <c r="E13" s="12">
+        <f>SUM(E2:E12)</f>
+        <v>79</v>
+      </c>
+      <c r="F13" s="12">
+        <f>SUM(F2:F12)</f>
+        <v>40</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="str">
+        <f>DEC2HEX(F14)</f>
+        <v>28</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8">
-        <f>F12*16</f>
-        <v>512</v>
-      </c>
-      <c r="E13" s="8">
-        <f t="shared" ref="E13" si="8">QUOTIENT(D13+7,8)</f>
-        <v>64</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" ref="F13" si="9">QUOTIENT(E13+1,2)</f>
-        <v>32</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8">
+        <f>F13*16</f>
+        <v>640</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" ref="E14" si="8">QUOTIENT(D14+7,8)</f>
+        <v>80</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" ref="F14" si="9">QUOTIENT(E14+1,2)</f>
+        <v>40</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5603,22 +5652,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5627,7 +5676,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5635,7 +5684,7 @@
         <v>400</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="64">
         <v>15</v>
@@ -5652,13 +5701,13 @@
         <v>1</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5666,7 +5715,7 @@
         <v>400</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="64">
         <v>14</v>
@@ -5683,13 +5732,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I3" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -5697,7 +5746,7 @@
         <v>400</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="64">
         <v>13</v>
@@ -5714,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>615</v>
+        <v>707</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I4" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5728,7 +5777,7 @@
         <v>400</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="64">
         <v>12</v>
@@ -5745,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I5" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -5759,7 +5808,7 @@
         <v>400</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="64">
         <v>11</v>
@@ -5776,13 +5825,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I6" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5790,7 +5839,7 @@
         <v>400</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="64">
         <v>10</v>
@@ -5807,13 +5856,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="70" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I7" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -5821,7 +5870,7 @@
         <v>400</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="64">
         <v>9</v>
@@ -5838,21 +5887,21 @@
         <v>1</v>
       </c>
       <c r="G8" s="71" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I8" s="74" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="120">
         <v>400</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C9" s="64">
         <v>8</v>
@@ -5869,13 +5918,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="72" t="s">
-        <v>682</v>
+        <v>25</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I9" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5883,7 +5932,7 @@
         <v>400</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="64">
         <v>7</v>
@@ -5900,13 +5949,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="71" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I10" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5914,7 +5963,7 @@
         <v>400</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" s="64">
         <v>6</v>
@@ -5931,13 +5980,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="71" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I11" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -5945,7 +5994,7 @@
         <v>400</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="64">
         <v>5</v>
@@ -5962,13 +6011,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="71" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I12" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5976,7 +6025,7 @@
         <v>400</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="64">
         <v>4</v>
@@ -5993,13 +6042,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I13" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6007,7 +6056,7 @@
         <v>400</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" s="64">
         <v>3</v>
@@ -6024,13 +6073,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I14" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6038,7 +6087,7 @@
         <v>400</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" s="64">
         <v>2</v>
@@ -6055,13 +6104,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I15" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6069,7 +6118,7 @@
         <v>400</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="64">
         <v>1</v>
@@ -6086,13 +6135,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="71" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I16" s="74" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6100,7 +6149,7 @@
         <v>400</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="65">
         <v>0</v>
@@ -6117,13 +6166,13 @@
         <v>1</v>
       </c>
       <c r="G17" s="73" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I17" s="94" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6132,10 +6181,10 @@
         <v>401</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D18" s="68">
         <v>16</v>
@@ -6149,13 +6198,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -6164,7 +6213,7 @@
         <v>402</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>26</v>
+        <v>712</v>
       </c>
       <c r="C19" s="64">
         <v>15</v>
@@ -6181,11 +6230,11 @@
         <v>1</v>
       </c>
       <c r="G19" s="78" t="s">
-        <v>26</v>
+        <v>715</v>
       </c>
       <c r="H19" s="78"/>
       <c r="I19" s="15" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -6193,7 +6242,7 @@
         <v>402</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>26</v>
+        <v>713</v>
       </c>
       <c r="C20" s="64">
         <v>14</v>
@@ -6210,11 +6259,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>26</v>
+        <v>714</v>
       </c>
       <c r="H20" s="34"/>
       <c r="I20" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6222,7 +6271,7 @@
         <v>402</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C21" s="64">
         <v>13</v>
@@ -6239,11 +6288,11 @@
         <v>1</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H21" s="59"/>
       <c r="I21" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -6272,7 +6321,7 @@
       </c>
       <c r="H22" s="59"/>
       <c r="I22" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -6301,7 +6350,7 @@
       </c>
       <c r="H23" s="59"/>
       <c r="I23" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -6330,7 +6379,7 @@
       </c>
       <c r="H24" s="59"/>
       <c r="I24" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -6338,10 +6387,10 @@
         <v>402</v>
       </c>
       <c r="B25" s="75" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D25" s="8">
         <v>2</v>
@@ -6355,13 +6404,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="79" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -6369,10 +6418,10 @@
         <v>402</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D26" s="8">
         <v>2</v>
@@ -6386,13 +6435,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="79" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -6400,7 +6449,7 @@
         <v>402</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" s="64">
         <v>5</v>
@@ -6417,13 +6466,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="79" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -6431,7 +6480,7 @@
         <v>402</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="64">
         <v>4</v>
@@ -6448,13 +6497,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -6462,7 +6511,7 @@
         <v>402</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" s="64">
         <v>3</v>
@@ -6479,13 +6528,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -6514,7 +6563,7 @@
       </c>
       <c r="H30" s="59"/>
       <c r="I30" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -6543,7 +6592,7 @@
       </c>
       <c r="H31" s="59"/>
       <c r="I31" s="19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6551,7 +6600,7 @@
         <v>402</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C32" s="95">
         <v>0</v>
@@ -6568,13 +6617,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>619</v>
+        <v>708</v>
       </c>
       <c r="H32" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6582,10 +6631,10 @@
         <v>403</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D33" s="68">
         <v>16</v>
@@ -6599,11 +6648,11 @@
         <v>1</v>
       </c>
       <c r="G33" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H33" s="50"/>
       <c r="I33" s="42" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -6614,7 +6663,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D34" s="8">
         <v>5</v>
@@ -6628,11 +6677,11 @@
         <v>1</v>
       </c>
       <c r="G34" s="86" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H34" s="51"/>
       <c r="I34" s="15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6640,10 +6689,10 @@
         <v>404</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D35" s="16">
         <v>10</v>
@@ -6657,13 +6706,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6671,7 +6720,7 @@
         <v>404</v>
       </c>
       <c r="B36" s="98" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C36" s="95">
         <v>0</v>
@@ -6688,13 +6737,13 @@
         <v>1</v>
       </c>
       <c r="G36" s="99" t="s">
-        <v>87</v>
+        <v>709</v>
       </c>
       <c r="H36" s="60" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -6705,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D37" s="8">
         <v>6</v>
@@ -6719,11 +6768,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="86" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H37" s="51"/>
       <c r="I37" s="15" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6731,10 +6780,10 @@
         <v>405</v>
       </c>
       <c r="B38" s="98" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C38" s="97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D38" s="66">
         <v>10</v>
@@ -6748,13 +6797,13 @@
         <v>1</v>
       </c>
       <c r="G38" s="99" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="H38" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -6765,7 +6814,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D39" s="8">
         <v>5</v>
@@ -6783,7 +6832,7 @@
       </c>
       <c r="H39" s="51"/>
       <c r="I39" s="15" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6791,10 +6840,10 @@
         <v>406</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D40" s="16">
         <v>10</v>
@@ -6808,13 +6857,13 @@
         <v>1</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6822,7 +6871,7 @@
         <v>406</v>
       </c>
       <c r="B41" s="98" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C41" s="95">
         <v>0</v>
@@ -6839,13 +6888,13 @@
         <v>1</v>
       </c>
       <c r="G41" s="99" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H41" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I41" s="41" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -6856,7 +6905,7 @@
         <v>26</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D42" s="8">
         <v>6</v>
@@ -6874,7 +6923,7 @@
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="15" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6882,10 +6931,10 @@
         <v>407</v>
       </c>
       <c r="B43" s="98" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D43" s="66">
         <v>10</v>
@@ -6899,13 +6948,13 @@
         <v>1</v>
       </c>
       <c r="G43" s="99" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H43" s="101" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="I43" s="41" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6916,7 +6965,7 @@
         <v>26</v>
       </c>
       <c r="C44" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D44" s="68">
         <v>16</v>
@@ -6934,7 +6983,7 @@
       </c>
       <c r="H44" s="50"/>
       <c r="I44" s="42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -6942,7 +6991,7 @@
         <v>409</v>
       </c>
       <c r="B45" s="83" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="C45" s="64">
         <v>15</v>
@@ -6959,13 +7008,13 @@
         <v>1</v>
       </c>
       <c r="G45" s="88" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -6973,7 +7022,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C46" s="100">
         <v>14</v>
@@ -6990,13 +7039,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H46" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -7004,7 +7053,7 @@
         <v>409</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C47" s="100">
         <v>13</v>
@@ -7021,13 +7070,13 @@
         <v>1</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -7035,7 +7084,7 @@
         <v>409</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C48" s="100">
         <v>12</v>
@@ -7052,13 +7101,13 @@
         <v>1</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H48" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -7066,7 +7115,7 @@
         <v>409</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C49" s="100">
         <v>11</v>
@@ -7083,13 +7132,13 @@
         <v>1</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -7097,7 +7146,7 @@
         <v>409</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="C50" s="100">
         <v>10</v>
@@ -7114,13 +7163,13 @@
         <v>1</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H50" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -7128,7 +7177,7 @@
         <v>409</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="C51" s="100">
         <v>9</v>
@@ -7145,13 +7194,13 @@
         <v>1</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -7159,7 +7208,7 @@
         <v>409</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="C52" s="100">
         <v>8</v>
@@ -7176,13 +7225,13 @@
         <v>1</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -7190,7 +7239,7 @@
         <v>409</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="C53" s="100">
         <v>7</v>
@@ -7207,13 +7256,13 @@
         <v>1</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -7221,7 +7270,7 @@
         <v>409</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C54" s="100">
         <v>6</v>
@@ -7238,13 +7287,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H54" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -7252,7 +7301,7 @@
         <v>409</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="C55" s="100">
         <v>5</v>
@@ -7269,13 +7318,13 @@
         <v>1</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -7283,7 +7332,7 @@
         <v>409</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C56" s="100">
         <v>4</v>
@@ -7300,13 +7349,13 @@
         <v>1</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H56" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -7314,7 +7363,7 @@
         <v>409</v>
       </c>
       <c r="B57" s="29" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C57" s="100">
         <v>3</v>
@@ -7331,13 +7380,13 @@
         <v>1</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -7345,7 +7394,7 @@
         <v>409</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="C58" s="100">
         <v>2</v>
@@ -7362,13 +7411,13 @@
         <v>1</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H58" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -7376,7 +7425,7 @@
         <v>409</v>
       </c>
       <c r="B59" s="29" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="C59" s="100">
         <v>1</v>
@@ -7393,13 +7442,13 @@
         <v>1</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -7407,7 +7456,7 @@
         <v>409</v>
       </c>
       <c r="B60" s="84" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="C60" s="64">
         <v>0</v>
@@ -7424,24 +7473,24 @@
         <v>1</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="H60" s="101" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="151" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B61" s="152" t="s">
         <v>26</v>
       </c>
       <c r="C61" s="102" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D61" s="103">
         <v>8</v>
@@ -7458,18 +7507,18 @@
         <v>25</v>
       </c>
       <c r="H61" s="154" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I61" s="155" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="C62" s="64">
         <v>7</v>
@@ -7486,21 +7535,21 @@
         <v>1</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="C63" s="64">
         <v>6</v>
@@ -7517,21 +7566,21 @@
         <v>1</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H63" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="C64" s="64">
         <v>5</v>
@@ -7548,21 +7597,21 @@
         <v>1</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="C65" s="64">
         <v>4</v>
@@ -7579,21 +7628,21 @@
         <v>1</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H65" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="C66" s="64">
         <v>3</v>
@@ -7610,21 +7659,21 @@
         <v>1</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="C67" s="64">
         <v>2</v>
@@ -7641,21 +7690,21 @@
         <v>1</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H67" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="120" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="C68" s="64">
         <v>1</v>
@@ -7672,21 +7721,21 @@
         <v>1</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="122" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B69" s="153" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="C69" s="95">
         <v>0</v>
@@ -7703,21 +7752,21 @@
         <v>1</v>
       </c>
       <c r="G69" s="46" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H69" s="101" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I69" s="46" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A70" s="142" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B70" s="43" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="C70" s="64">
         <v>15</v>
@@ -7734,21 +7783,21 @@
         <v>1</v>
       </c>
       <c r="G70" s="44" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="120" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B71" s="77" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C71" s="64">
         <v>14</v>
@@ -7765,21 +7814,21 @@
         <v>1</v>
       </c>
       <c r="G71" s="90" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H71" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="120" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B72" s="77" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C72" s="64">
         <v>13</v>
@@ -7796,18 +7845,18 @@
         <v>1</v>
       </c>
       <c r="G72" s="90" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H72" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I72" s="15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="120" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B73" s="77" t="s">
         <v>26</v>
@@ -7831,18 +7880,18 @@
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="122" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B74" s="82" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C74" s="97" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D74" s="66">
         <v>12</v>
@@ -7856,24 +7905,24 @@
         <v>1</v>
       </c>
       <c r="G74" s="87" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H74" s="101" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I74" s="41" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="150" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B75" s="85" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C75" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D75" s="68">
         <v>16</v>
@@ -7887,21 +7936,21 @@
         <v>1</v>
       </c>
       <c r="G75" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I75" s="42" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A76" s="142" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B76" s="43" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="C76" s="64">
         <v>15</v>
@@ -7918,21 +7967,21 @@
         <v>1</v>
       </c>
       <c r="G76" s="88" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="H76" s="51" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I76" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="120" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B77" s="77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C77" s="64">
         <v>14</v>
@@ -7949,21 +7998,21 @@
         <v>1</v>
       </c>
       <c r="G77" s="91" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H77" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="120" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B78" s="77" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C78" s="64">
         <v>13</v>
@@ -7980,18 +8029,18 @@
         <v>1</v>
       </c>
       <c r="G78" s="89" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H78" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I78" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="120" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B79" s="77" t="s">
         <v>26</v>
@@ -8015,18 +8064,18 @@
       </c>
       <c r="H79" s="59"/>
       <c r="I79" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="122" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C80" s="97" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D80" s="66">
         <v>12</v>
@@ -8040,24 +8089,24 @@
         <v>1</v>
       </c>
       <c r="G80" s="87" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H80" s="101" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I80" s="41" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="150" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B81" s="85" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C81" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D81" s="68">
         <v>16</v>
@@ -8071,24 +8120,24 @@
         <v>1</v>
       </c>
       <c r="G81" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H81" s="50" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="142" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C82" s="63" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D82" s="8">
         <v>8</v>
@@ -8102,24 +8151,24 @@
         <v>1</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H82" s="51" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I82" s="15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="120" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B83" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C83" s="96" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D83" s="16">
         <v>3</v>
@@ -8137,15 +8186,15 @@
       </c>
       <c r="H83" s="59"/>
       <c r="I83" s="15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="120" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B84" s="29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C84" s="100">
         <v>4</v>
@@ -8162,24 +8211,24 @@
         <v>1</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H84" s="59" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I84" s="15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B85" s="37" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C85" s="97" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D85" s="66">
         <v>4</v>
@@ -8193,13 +8242,13 @@
         <v>1</v>
       </c>
       <c r="G85" s="46" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H85" s="101" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I85" s="46" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -8210,7 +8259,7 @@
         <v>26</v>
       </c>
       <c r="C86" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D86" s="68">
         <v>16</v>
@@ -8228,7 +8277,7 @@
       </c>
       <c r="H86" s="50"/>
       <c r="I86" s="42" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8236,7 +8285,7 @@
         <v>411</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C87" s="64">
         <v>15</v>
@@ -8253,13 +8302,13 @@
         <v>1</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H87" s="51" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I87" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -8267,7 +8316,7 @@
         <v>411</v>
       </c>
       <c r="B88" s="29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C88" s="100">
         <v>14</v>
@@ -8284,13 +8333,13 @@
         <v>1</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="H88" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8298,10 +8347,10 @@
         <v>411</v>
       </c>
       <c r="B89" s="29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C89" s="96" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D89" s="16">
         <v>2</v>
@@ -8315,13 +8364,13 @@
         <v>1</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H89" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -8329,7 +8378,7 @@
         <v>411</v>
       </c>
       <c r="B90" s="29" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C90" s="100">
         <v>11</v>
@@ -8346,13 +8395,13 @@
         <v>1</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="H90" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8360,10 +8409,10 @@
         <v>411</v>
       </c>
       <c r="B91" s="29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C91" s="96" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D91" s="16">
         <v>2</v>
@@ -8377,13 +8426,13 @@
         <v>1</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H91" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I91" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -8391,7 +8440,7 @@
         <v>411</v>
       </c>
       <c r="B92" s="29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C92" s="100">
         <v>8</v>
@@ -8408,13 +8457,13 @@
         <v>1</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="H92" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I92" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8422,10 +8471,10 @@
         <v>411</v>
       </c>
       <c r="B93" s="29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C93" s="96" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D93" s="16">
         <v>2</v>
@@ -8439,13 +8488,13 @@
         <v>1</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H93" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I93" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -8453,7 +8502,7 @@
         <v>411</v>
       </c>
       <c r="B94" s="29" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C94" s="100">
         <v>5</v>
@@ -8470,13 +8519,13 @@
         <v>1</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="H94" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8484,10 +8533,10 @@
         <v>411</v>
       </c>
       <c r="B95" s="29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C95" s="96" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D95" s="16">
         <v>2</v>
@@ -8501,13 +8550,13 @@
         <v>1</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H95" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I95" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -8515,7 +8564,7 @@
         <v>411</v>
       </c>
       <c r="B96" s="29" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C96" s="100">
         <v>2</v>
@@ -8532,13 +8581,13 @@
         <v>1</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="H96" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I96" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -8546,10 +8595,10 @@
         <v>411</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C97" s="97" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D97" s="66">
         <v>2</v>
@@ -8563,13 +8612,13 @@
         <v>1</v>
       </c>
       <c r="G97" s="46" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H97" s="101" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I97" s="46" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8577,10 +8626,10 @@
         <v>412</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C98" s="63" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D98" s="8">
         <v>2</v>
@@ -8594,13 +8643,13 @@
         <v>1</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H98" s="51" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -8608,7 +8657,7 @@
         <v>412</v>
       </c>
       <c r="B99" s="29" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C99" s="100">
         <v>13</v>
@@ -8625,13 +8674,13 @@
         <v>1</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="H99" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I99" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8639,10 +8688,10 @@
         <v>412</v>
       </c>
       <c r="B100" s="29" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C100" s="96" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D100" s="16">
         <v>2</v>
@@ -8656,13 +8705,13 @@
         <v>1</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H100" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I100" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -8670,7 +8719,7 @@
         <v>412</v>
       </c>
       <c r="B101" s="29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C101" s="100">
         <v>10</v>
@@ -8687,13 +8736,13 @@
         <v>1</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="H101" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I101" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8701,10 +8750,10 @@
         <v>412</v>
       </c>
       <c r="B102" s="29" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C102" s="96" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D102" s="16">
         <v>2</v>
@@ -8718,13 +8767,13 @@
         <v>1</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H102" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I102" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -8732,7 +8781,7 @@
         <v>412</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C103" s="100">
         <v>7</v>
@@ -8749,13 +8798,13 @@
         <v>1</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="H103" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I103" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8763,10 +8812,10 @@
         <v>412</v>
       </c>
       <c r="B104" s="29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C104" s="96" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D104" s="16">
         <v>2</v>
@@ -8780,13 +8829,13 @@
         <v>1</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H104" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I104" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -8794,7 +8843,7 @@
         <v>412</v>
       </c>
       <c r="B105" s="29" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C105" s="100">
         <v>4</v>
@@ -8811,13 +8860,13 @@
         <v>1</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="H105" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I105" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8825,10 +8874,10 @@
         <v>412</v>
       </c>
       <c r="B106" s="29" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C106" s="96" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D106" s="16">
         <v>2</v>
@@ -8842,13 +8891,13 @@
         <v>1</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H106" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I106" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -8856,7 +8905,7 @@
         <v>412</v>
       </c>
       <c r="B107" s="29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C107" s="100">
         <v>1</v>
@@ -8873,13 +8922,13 @@
         <v>1</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="H107" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I107" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -8887,7 +8936,7 @@
         <v>412</v>
       </c>
       <c r="B108" s="37" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C108" s="95">
         <v>0</v>
@@ -8904,13 +8953,13 @@
         <v>1</v>
       </c>
       <c r="G108" s="46" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H108" s="101" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I108" s="46" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -8918,10 +8967,10 @@
         <v>413</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C109" s="63" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D109" s="8">
         <v>3</v>
@@ -8935,13 +8984,13 @@
         <v>1</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H109" s="51" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I109" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -8952,7 +9001,7 @@
         <v>26</v>
       </c>
       <c r="C110" s="96" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D110" s="16">
         <v>3</v>
@@ -8970,7 +9019,7 @@
       </c>
       <c r="H110" s="59"/>
       <c r="I110" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -8978,7 +9027,7 @@
         <v>413</v>
       </c>
       <c r="B111" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C111" s="100">
         <v>9</v>
@@ -8995,13 +9044,13 @@
         <v>1</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="H111" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I111" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -9009,7 +9058,7 @@
         <v>413</v>
       </c>
       <c r="B112" s="29" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C112" s="100">
         <v>8</v>
@@ -9026,13 +9075,13 @@
         <v>1</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H112" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I112" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -9040,7 +9089,7 @@
         <v>413</v>
       </c>
       <c r="B113" s="29" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C113" s="100">
         <v>7</v>
@@ -9057,13 +9106,13 @@
         <v>1</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="H113" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I113" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -9071,7 +9120,7 @@
         <v>413</v>
       </c>
       <c r="B114" s="29" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C114" s="100">
         <v>6</v>
@@ -9088,13 +9137,13 @@
         <v>1</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="H114" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I114" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -9102,10 +9151,10 @@
         <v>413</v>
       </c>
       <c r="B115" s="29" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C115" s="96" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D115" s="16">
         <v>2</v>
@@ -9119,13 +9168,13 @@
         <v>1</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H115" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -9133,7 +9182,7 @@
         <v>413</v>
       </c>
       <c r="B116" s="29" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C116" s="100">
         <v>3</v>
@@ -9150,13 +9199,13 @@
         <v>1</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="H116" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I116" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -9164,10 +9213,10 @@
         <v>413</v>
       </c>
       <c r="B117" s="29" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C117" s="96" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D117" s="16">
         <v>2</v>
@@ -9181,13 +9230,13 @@
         <v>1</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H117" s="59" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I117" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9195,7 +9244,7 @@
         <v>413</v>
       </c>
       <c r="B118" s="37" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C118" s="95">
         <v>0</v>
@@ -9212,13 +9261,13 @@
         <v>1</v>
       </c>
       <c r="G118" s="46" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="H118" s="101" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I118" s="46" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -9226,7 +9275,7 @@
         <v>414</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="C119" s="64">
         <v>15</v>
@@ -9243,13 +9292,13 @@
         <v>1</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="H119" s="51" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I119" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -9257,7 +9306,7 @@
         <v>414</v>
       </c>
       <c r="B120" s="29" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C120" s="100">
         <v>14</v>
@@ -9274,13 +9323,13 @@
         <v>1</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H120" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I120" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -9288,7 +9337,7 @@
         <v>414</v>
       </c>
       <c r="B121" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C121" s="100">
         <v>13</v>
@@ -9305,13 +9354,13 @@
         <v>1</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H121" s="59" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I121" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -9340,7 +9389,7 @@
       </c>
       <c r="H122" s="59"/>
       <c r="I122" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9348,10 +9397,10 @@
         <v>414</v>
       </c>
       <c r="B123" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C123" s="97" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D123" s="66">
         <v>12</v>
@@ -9365,13 +9414,13 @@
         <v>1</v>
       </c>
       <c r="G123" s="46" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H123" s="101" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I123" s="46" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9379,10 +9428,10 @@
         <v>415</v>
       </c>
       <c r="B124" s="40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C124" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D124" s="68">
         <v>16</v>
@@ -9396,13 +9445,13 @@
         <v>1</v>
       </c>
       <c r="G124" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H124" s="50" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I124" s="42" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9410,10 +9459,10 @@
         <v>416</v>
       </c>
       <c r="B125" s="40" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C125" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D125" s="68">
         <v>16</v>
@@ -9427,13 +9476,13 @@
         <v>1</v>
       </c>
       <c r="G125" s="42" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="H125" s="50" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="I125" s="42" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9444,7 +9493,7 @@
         <v>26</v>
       </c>
       <c r="C126" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D126" s="68">
         <v>16</v>
@@ -9461,10 +9510,10 @@
         <v>26</v>
       </c>
       <c r="H126" s="50" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="I126" s="42" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -9475,7 +9524,7 @@
         <v>26</v>
       </c>
       <c r="C127" s="63" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D127" s="8">
         <v>5</v>
@@ -9493,7 +9542,7 @@
       </c>
       <c r="H127" s="51"/>
       <c r="I127" s="15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -9501,10 +9550,10 @@
         <v>418</v>
       </c>
       <c r="B128" s="29" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C128" s="96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D128" s="16">
         <v>10</v>
@@ -9518,13 +9567,13 @@
         <v>1</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H128" s="59" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I128" s="15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -9532,7 +9581,7 @@
         <v>418</v>
       </c>
       <c r="B129" s="37" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C129" s="95">
         <v>0</v>
@@ -9549,13 +9598,13 @@
         <v>1</v>
       </c>
       <c r="G129" s="46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H129" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I129" s="46" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -9566,7 +9615,7 @@
         <v>26</v>
       </c>
       <c r="C130" s="63" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D130" s="8">
         <v>6</v>
@@ -9584,7 +9633,7 @@
       </c>
       <c r="H130" s="51"/>
       <c r="I130" s="15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -9592,10 +9641,10 @@
         <v>419</v>
       </c>
       <c r="B131" s="37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C131" s="97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D131" s="66">
         <v>10</v>
@@ -9609,24 +9658,24 @@
         <v>1</v>
       </c>
       <c r="G131" s="46" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="H131" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I131" s="46" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="142" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C132" s="63" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D132" s="8">
         <v>5</v>
@@ -9644,18 +9693,18 @@
       </c>
       <c r="H132" s="51"/>
       <c r="I132" s="15" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" s="120" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B133" s="29" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C133" s="96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D133" s="16">
         <v>10</v>
@@ -9669,21 +9718,21 @@
         <v>1</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H133" s="59" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I133" s="15" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="122" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B134" s="37" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C134" s="95">
         <v>0</v>
@@ -9700,24 +9749,24 @@
         <v>1</v>
       </c>
       <c r="G134" s="46" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H134" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I134" s="46" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="142" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C135" s="63" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D135" s="8">
         <v>6</v>
@@ -9735,18 +9784,18 @@
       </c>
       <c r="H135" s="51"/>
       <c r="I135" s="15" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="122" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B136" s="37" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C136" s="97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D136" s="66">
         <v>10</v>
@@ -9760,24 +9809,24 @@
         <v>1</v>
       </c>
       <c r="G136" s="46" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="H136" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I136" s="46" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="142" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C137" s="63" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D137" s="8">
         <v>5</v>
@@ -9795,18 +9844,18 @@
       </c>
       <c r="H137" s="51"/>
       <c r="I137" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="120" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B138" s="29" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C138" s="96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D138" s="16">
         <v>10</v>
@@ -9820,21 +9869,21 @@
         <v>1</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H138" s="59" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I138" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="122" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B139" s="37" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C139" s="95">
         <v>0</v>
@@ -9851,24 +9900,24 @@
         <v>1</v>
       </c>
       <c r="G139" s="46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H139" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I139" s="46" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="142" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C140" s="63" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D140" s="8">
         <v>6</v>
@@ -9886,18 +9935,18 @@
       </c>
       <c r="H140" s="51"/>
       <c r="I140" s="15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="122" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B141" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C141" s="97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D141" s="66">
         <v>10</v>
@@ -9911,24 +9960,24 @@
         <v>1</v>
       </c>
       <c r="G141" s="46" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="H141" s="101" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I141" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="150" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B142" s="105" t="s">
         <v>26</v>
       </c>
       <c r="C142" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D142" s="68">
         <v>16</v>
@@ -9946,18 +9995,18 @@
       </c>
       <c r="H142" s="50"/>
       <c r="I142" s="42" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="114" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B143" s="45" t="s">
         <v>26</v>
       </c>
       <c r="C143" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D143" s="93">
         <v>16</v>
@@ -9975,7 +10024,7 @@
       </c>
       <c r="H143" s="60"/>
       <c r="I143" s="41" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -10027,22 +10076,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -10051,7 +10100,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10059,10 +10108,10 @@
         <v>420</v>
       </c>
       <c r="B2" s="144" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C2" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D2" s="144">
         <v>16</v>
@@ -10076,7 +10125,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="144" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H2" s="144"/>
       <c r="I2" s="144"/>
@@ -10086,10 +10135,10 @@
         <v>421</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C3" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D3" s="144">
         <v>16</v>
@@ -10103,7 +10152,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="144" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H3" s="144"/>
       <c r="I3" s="144"/>
@@ -10113,7 +10162,7 @@
         <v>422</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -10134,7 +10183,7 @@
       </c>
       <c r="H4" s="51"/>
       <c r="I4" s="51" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -10142,7 +10191,7 @@
         <v>422</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C5" s="59">
         <v>1</v>
@@ -10159,13 +10208,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10173,10 +10222,10 @@
         <v>422</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C6" s="96" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D6" s="59">
         <v>2</v>
@@ -10190,13 +10239,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10204,7 +10253,7 @@
         <v>422</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C7" s="59">
         <v>4</v>
@@ -10221,13 +10270,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -10235,10 +10284,10 @@
         <v>422</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C8" s="96" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D8" s="59">
         <v>2</v>
@@ -10252,13 +10301,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10266,7 +10315,7 @@
         <v>422</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C9" s="59">
         <v>7</v>
@@ -10283,13 +10332,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10297,7 +10346,7 @@
         <v>422</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C10" s="59">
         <v>8</v>
@@ -10314,13 +10363,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10328,7 +10377,7 @@
         <v>422</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C11" s="59">
         <v>9</v>
@@ -10345,13 +10394,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10359,7 +10408,7 @@
         <v>422</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C12" s="59">
         <v>10</v>
@@ -10376,13 +10425,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10390,7 +10439,7 @@
         <v>422</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C13" s="59">
         <v>11</v>
@@ -10407,13 +10456,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10421,7 +10470,7 @@
         <v>422</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C14" s="59">
         <v>12</v>
@@ -10438,13 +10487,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10452,7 +10501,7 @@
         <v>422</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C15" s="59">
         <v>13</v>
@@ -10469,13 +10518,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -10504,7 +10553,7 @@
       </c>
       <c r="H16" s="59"/>
       <c r="I16" s="59" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10533,7 +10582,7 @@
       </c>
       <c r="H17" s="101"/>
       <c r="I17" s="101" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10541,7 +10590,7 @@
         <v>423</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -10558,13 +10607,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10572,7 +10621,7 @@
         <v>423</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="59">
         <v>1</v>
@@ -10589,13 +10638,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -10603,7 +10652,7 @@
         <v>423</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C20" s="59">
         <v>2</v>
@@ -10620,13 +10669,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10634,7 +10683,7 @@
         <v>423</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C21" s="59">
         <v>3</v>
@@ -10651,13 +10700,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I21" s="59" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -10665,7 +10714,7 @@
         <v>423</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C22" s="59">
         <v>4</v>
@@ -10682,13 +10731,13 @@
         <v>1</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I22" s="59" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10696,7 +10745,7 @@
         <v>423</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C23" s="59">
         <v>5</v>
@@ -10713,13 +10762,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10727,7 +10776,7 @@
         <v>423</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C24" s="59">
         <v>6</v>
@@ -10744,13 +10793,13 @@
         <v>1</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="I24" s="59" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -10758,7 +10807,7 @@
         <v>423</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C25" s="59">
         <v>7</v>
@@ -10775,13 +10824,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="I25" s="59" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -10789,7 +10838,7 @@
         <v>423</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C26" s="59">
         <v>8</v>
@@ -10806,13 +10855,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="I26" s="59" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="120" x14ac:dyDescent="0.25">
@@ -10820,7 +10869,7 @@
         <v>423</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C27" s="59">
         <v>9</v>
@@ -10837,13 +10886,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="I27" s="59" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="165" x14ac:dyDescent="0.25">
@@ -10851,7 +10900,7 @@
         <v>423</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C28" s="59">
         <v>10</v>
@@ -10868,13 +10917,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="I28" s="59" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -10882,10 +10931,10 @@
         <v>423</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C29" s="96" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D29" s="59">
         <v>2</v>
@@ -10899,13 +10948,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="I29" s="59" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -10913,10 +10962,10 @@
         <v>423</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C30" s="96" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D30" s="59">
         <v>2</v>
@@ -10930,13 +10979,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -10944,7 +10993,7 @@
         <v>423</v>
       </c>
       <c r="B31" s="101" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C31" s="101">
         <v>15</v>
@@ -10961,13 +11010,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="66" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H31" s="112" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="I31" s="101" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10975,10 +11024,10 @@
         <v>424</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D32" s="144">
         <v>16</v>
@@ -10992,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="145" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
@@ -11002,10 +11051,10 @@
         <v>425</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D33" s="144">
         <v>16</v>
@@ -11019,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="145" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H33" s="50"/>
       <c r="I33" s="50"/>
@@ -11029,10 +11078,10 @@
         <v>426</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D34" s="144">
         <v>16</v>
@@ -11046,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="145" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H34" s="50"/>
       <c r="I34" s="50"/>
@@ -11056,10 +11105,10 @@
         <v>427</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D35" s="144">
         <v>16</v>
@@ -11073,7 +11122,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="145" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H35" s="50"/>
       <c r="I35" s="50"/>
@@ -11083,10 +11132,10 @@
         <v>428</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C36" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D36" s="144">
         <v>16</v>
@@ -11100,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="145" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H36" s="50"/>
       <c r="I36" s="50"/>
@@ -11110,10 +11159,10 @@
         <v>429</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D37" s="144">
         <v>16</v>
@@ -11127,20 +11176,20 @@
         <v>1</v>
       </c>
       <c r="G37" s="145" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H37" s="50"/>
       <c r="I37" s="50"/>
     </row>
     <row r="38" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="150" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D38" s="144">
         <v>16</v>
@@ -11154,20 +11203,20 @@
         <v>1</v>
       </c>
       <c r="G38" s="145" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H38" s="50"/>
       <c r="I38" s="50"/>
     </row>
     <row r="39" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="150" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D39" s="144">
         <v>16</v>
@@ -11181,20 +11230,20 @@
         <v>1</v>
       </c>
       <c r="G39" s="145" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H39" s="50"/>
       <c r="I39" s="50"/>
     </row>
     <row r="40" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="150" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B40" s="50" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D40" s="144">
         <v>16</v>
@@ -11208,20 +11257,20 @@
         <v>1</v>
       </c>
       <c r="G40" s="145" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H40" s="50"/>
       <c r="I40" s="50"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="150" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B41" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C41" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D41" s="144">
         <v>16</v>
@@ -11235,20 +11284,20 @@
         <v>1</v>
       </c>
       <c r="G41" s="145" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H41" s="50"/>
       <c r="I41" s="50"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="121" t="s">
+        <v>600</v>
+      </c>
+      <c r="B42" s="133" t="s">
+        <v>601</v>
+      </c>
+      <c r="C42" s="118" t="s">
         <v>603</v>
-      </c>
-      <c r="B42" s="133" t="s">
-        <v>604</v>
-      </c>
-      <c r="C42" s="118" t="s">
-        <v>606</v>
       </c>
       <c r="D42" s="133">
         <v>15</v>
@@ -11262,17 +11311,17 @@
         <v>1</v>
       </c>
       <c r="G42" s="134" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H42" s="135"/>
       <c r="I42" s="133"/>
     </row>
     <row r="43" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B43" s="136" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C43" s="136">
         <v>0</v>
@@ -11289,20 +11338,20 @@
         <v>1</v>
       </c>
       <c r="G43" s="137" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="H43" s="138"/>
       <c r="I43" s="136"/>
     </row>
     <row r="44" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="114" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B44" s="130" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C44" s="96" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D44" s="130">
         <v>16</v>
@@ -11316,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="131" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H44" s="132"/>
       <c r="I44" s="130"/>
@@ -11382,22 +11431,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -11406,7 +11455,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11417,7 +11466,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D2" s="101">
         <v>16</v>
@@ -11431,11 +11480,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H2" s="66"/>
       <c r="I2" s="101" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -11443,7 +11492,7 @@
         <v>431</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -11460,13 +11509,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I3" s="51" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -11491,11 +11540,11 @@
         <v>1</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="59" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11503,7 +11552,7 @@
         <v>431</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" s="59">
         <v>2</v>
@@ -11520,13 +11569,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -11534,7 +11583,7 @@
         <v>431</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="59">
         <v>3</v>
@@ -11551,13 +11600,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11565,7 +11614,7 @@
         <v>431</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C7" s="59">
         <v>4</v>
@@ -11582,13 +11631,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -11596,7 +11645,7 @@
         <v>431</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C8" s="59">
         <v>5</v>
@@ -11613,13 +11662,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11627,7 +11676,7 @@
         <v>431</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C9" s="59">
         <v>6</v>
@@ -11644,13 +11693,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -11675,11 +11724,11 @@
         <v>1</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="59" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -11704,11 +11753,11 @@
         <v>1</v>
       </c>
       <c r="G11" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" s="59" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11716,7 +11765,7 @@
         <v>431</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C12" s="59">
         <v>9</v>
@@ -11733,13 +11782,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11747,7 +11796,7 @@
         <v>431</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="C13" s="107">
         <v>0.46527777777777779</v>
@@ -11764,11 +11813,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="59" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11776,7 +11825,7 @@
         <v>431</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C14" s="59">
         <v>12</v>
@@ -11793,13 +11842,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11807,7 +11856,7 @@
         <v>431</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C15" s="59">
         <v>13</v>
@@ -11824,13 +11873,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11838,7 +11887,7 @@
         <v>431</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C16" s="59">
         <v>14</v>
@@ -11855,11 +11904,11 @@
         <v>1</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="59" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11884,11 +11933,11 @@
         <v>1</v>
       </c>
       <c r="G17" s="101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H17" s="66"/>
       <c r="I17" s="101" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11896,7 +11945,7 @@
         <v>432</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -11913,13 +11962,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="I18" s="51" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
@@ -11927,7 +11976,7 @@
         <v>432</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C19" s="59">
         <v>1</v>
@@ -11944,13 +11993,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -11961,7 +12010,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="108" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D20" s="59">
         <v>5</v>
@@ -11975,11 +12024,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="59" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -11987,10 +12036,10 @@
         <v>432</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="C21" s="108" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D21" s="59">
         <v>2</v>
@@ -12004,13 +12053,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I21" s="59" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -12021,7 +12070,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="108" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D22" s="59">
         <v>2</v>
@@ -12035,11 +12084,11 @@
         <v>1</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="59" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -12047,7 +12096,7 @@
         <v>432</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C23" s="59">
         <v>11</v>
@@ -12064,13 +12113,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -12078,7 +12127,7 @@
         <v>432</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C24" s="59">
         <v>12</v>
@@ -12099,7 +12148,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="59" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12107,10 +12156,10 @@
         <v>432</v>
       </c>
       <c r="B25" s="101" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D25" s="101">
         <v>3</v>
@@ -12124,13 +12173,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="66" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H25" s="66" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="I25" s="101" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12138,7 +12187,7 @@
         <v>433</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -12155,13 +12204,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -12172,7 +12221,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="108" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D27" s="59">
         <v>2</v>
@@ -12186,11 +12235,11 @@
         <v>1</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="59" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -12201,7 +12250,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="108" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D28" s="59">
         <v>3</v>
@@ -12215,11 +12264,11 @@
         <v>1</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="59" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12244,11 +12293,11 @@
         <v>1</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="59" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -12256,10 +12305,10 @@
         <v>433</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C30" s="108" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D30" s="59">
         <v>2</v>
@@ -12273,13 +12322,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -12287,7 +12336,7 @@
         <v>433</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C31" s="59">
         <v>9</v>
@@ -12304,13 +12353,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12318,7 +12367,7 @@
         <v>433</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C32" s="59">
         <v>10</v>
@@ -12335,11 +12384,11 @@
         <v>1</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="59" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -12347,7 +12396,7 @@
         <v>433</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C33" s="59">
         <v>11</v>
@@ -12364,13 +12413,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -12378,7 +12427,7 @@
         <v>433</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C34" s="59">
         <v>12</v>
@@ -12395,13 +12444,13 @@
         <v>1</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="I34" s="59" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12409,7 +12458,7 @@
         <v>433</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C35" s="59">
         <v>13</v>
@@ -12426,13 +12475,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12443,7 +12492,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D36" s="101">
         <v>2</v>
@@ -12457,11 +12506,11 @@
         <v>1</v>
       </c>
       <c r="G36" s="101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H36" s="66"/>
       <c r="I36" s="101" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -12472,7 +12521,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="110" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D37" s="51">
         <v>3</v>
@@ -12486,11 +12535,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="111" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="59" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -12515,11 +12564,11 @@
         <v>1</v>
       </c>
       <c r="G38" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H38" s="16"/>
       <c r="I38" s="59" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -12530,7 +12579,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="108" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D39" s="59">
         <v>2</v>
@@ -12544,11 +12593,11 @@
         <v>1</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H39" s="16"/>
       <c r="I39" s="59" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12556,7 +12605,7 @@
         <v>434</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C40" s="59">
         <v>6</v>
@@ -12573,11 +12622,11 @@
         <v>1</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="59" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -12585,7 +12634,7 @@
         <v>434</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C41" s="59">
         <v>7</v>
@@ -12602,11 +12651,11 @@
         <v>1</v>
       </c>
       <c r="G41" s="59" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H41" s="16"/>
       <c r="I41" s="59" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -12614,7 +12663,7 @@
         <v>434</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C42" s="59">
         <v>8</v>
@@ -12631,11 +12680,11 @@
         <v>1</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H42" s="16"/>
       <c r="I42" s="59" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -12643,7 +12692,7 @@
         <v>434</v>
       </c>
       <c r="B43" s="59" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C43" s="59">
         <v>9</v>
@@ -12660,11 +12709,11 @@
         <v>1</v>
       </c>
       <c r="G43" s="59" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="59" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12672,7 +12721,7 @@
         <v>434</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C44" s="59">
         <v>10</v>
@@ -12689,11 +12738,11 @@
         <v>1</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H44" s="16"/>
       <c r="I44" s="59" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -12701,7 +12750,7 @@
         <v>434</v>
       </c>
       <c r="B45" s="59" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C45" s="59">
         <v>11</v>
@@ -12718,11 +12767,11 @@
         <v>1</v>
       </c>
       <c r="G45" s="59" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H45" s="16"/>
       <c r="I45" s="59" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12733,7 +12782,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D46" s="101">
         <v>4</v>
@@ -12747,11 +12796,11 @@
         <v>1</v>
       </c>
       <c r="G46" s="101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H46" s="66"/>
       <c r="I46" s="101" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12762,7 +12811,7 @@
         <v>26</v>
       </c>
       <c r="C47" s="67" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D47" s="50">
         <v>16</v>
@@ -12776,11 +12825,11 @@
         <v>1</v>
       </c>
       <c r="G47" s="50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H47" s="68"/>
       <c r="I47" s="101" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -12805,11 +12854,11 @@
         <v>1</v>
       </c>
       <c r="G48" s="51" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -12834,11 +12883,11 @@
         <v>1</v>
       </c>
       <c r="G49" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H49" s="16"/>
       <c r="I49" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -12863,11 +12912,11 @@
         <v>1</v>
       </c>
       <c r="G50" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H50" s="16"/>
       <c r="I50" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -12892,11 +12941,11 @@
         <v>1</v>
       </c>
       <c r="G51" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H51" s="16"/>
       <c r="I51" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12904,7 +12953,7 @@
         <v>436</v>
       </c>
       <c r="B52" s="59" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C52" s="59">
         <v>4</v>
@@ -12921,11 +12970,11 @@
         <v>1</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H52" s="16"/>
       <c r="I52" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -12950,11 +12999,11 @@
         <v>1</v>
       </c>
       <c r="G53" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H53" s="16"/>
       <c r="I53" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -12979,11 +13028,11 @@
         <v>1</v>
       </c>
       <c r="G54" s="59" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H54" s="16"/>
       <c r="I54" s="59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -12991,7 +13040,7 @@
         <v>436</v>
       </c>
       <c r="B55" s="59" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C55" s="59">
         <v>7</v>
@@ -13008,11 +13057,11 @@
         <v>1</v>
       </c>
       <c r="G55" s="59" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H55" s="16"/>
       <c r="I55" s="59" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -13020,7 +13069,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C56" s="59">
         <v>8</v>
@@ -13037,11 +13086,11 @@
         <v>1</v>
       </c>
       <c r="G56" s="59" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H56" s="16"/>
       <c r="I56" s="59" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -13049,7 +13098,7 @@
         <v>436</v>
       </c>
       <c r="B57" s="59" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C57" s="59">
         <v>9</v>
@@ -13066,11 +13115,11 @@
         <v>1</v>
       </c>
       <c r="G57" s="59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="59" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13078,7 +13127,7 @@
         <v>436</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C58" s="59">
         <v>10</v>
@@ -13095,11 +13144,11 @@
         <v>1</v>
       </c>
       <c r="G58" s="59" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H58" s="16"/>
       <c r="I58" s="59" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -13107,7 +13156,7 @@
         <v>436</v>
       </c>
       <c r="B59" s="59" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C59" s="59">
         <v>11</v>
@@ -13124,11 +13173,11 @@
         <v>1</v>
       </c>
       <c r="G59" s="59" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H59" s="16"/>
       <c r="I59" s="59" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -13136,7 +13185,7 @@
         <v>436</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C60" s="59">
         <v>12</v>
@@ -13153,11 +13202,11 @@
         <v>1</v>
       </c>
       <c r="G60" s="59" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="59" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -13165,7 +13214,7 @@
         <v>436</v>
       </c>
       <c r="B61" s="59" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C61" s="59">
         <v>13</v>
@@ -13182,11 +13231,11 @@
         <v>1</v>
       </c>
       <c r="G61" s="59" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H61" s="16"/>
       <c r="I61" s="59" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -13194,7 +13243,7 @@
         <v>436</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C62" s="59">
         <v>14</v>
@@ -13211,11 +13260,11 @@
         <v>1</v>
       </c>
       <c r="G62" s="59" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H62" s="16"/>
       <c r="I62" s="59" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13240,11 +13289,11 @@
         <v>1</v>
       </c>
       <c r="G63" s="101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H63" s="66"/>
       <c r="I63" s="101" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13269,11 +13318,11 @@
         <v>1</v>
       </c>
       <c r="G64" s="50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H64" s="68"/>
       <c r="I64" s="50" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -13281,10 +13330,10 @@
         <v>438</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C65" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D65" s="60">
         <v>16</v>
@@ -13298,7 +13347,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H65" s="93"/>
       <c r="I65" s="60"/>
@@ -13308,10 +13357,10 @@
         <v>439</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D66" s="60">
         <v>16</v>
@@ -13325,20 +13374,20 @@
         <v>1</v>
       </c>
       <c r="G66" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H66" s="93"/>
       <c r="I66" s="60"/>
     </row>
     <row r="67" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="114" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D67" s="60">
         <v>16</v>
@@ -13352,20 +13401,20 @@
         <v>1</v>
       </c>
       <c r="G67" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H67" s="93"/>
       <c r="I67" s="60"/>
     </row>
     <row r="68" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="114" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D68" s="60">
         <v>16</v>
@@ -13379,20 +13428,20 @@
         <v>1</v>
       </c>
       <c r="G68" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H68" s="93"/>
       <c r="I68" s="60"/>
     </row>
     <row r="69" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="114" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B69" s="60" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D69" s="60">
         <v>16</v>
@@ -13406,20 +13455,20 @@
         <v>1</v>
       </c>
       <c r="G69" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H69" s="93"/>
       <c r="I69" s="60"/>
     </row>
     <row r="70" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="114" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B70" s="60" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D70" s="60">
         <v>16</v>
@@ -13433,20 +13482,20 @@
         <v>1</v>
       </c>
       <c r="G70" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H70" s="93"/>
       <c r="I70" s="60"/>
     </row>
     <row r="71" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="114" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B71" s="60" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C71" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D71" s="60">
         <v>16</v>
@@ -13460,20 +13509,20 @@
         <v>1</v>
       </c>
       <c r="G71" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H71" s="93"/>
       <c r="I71" s="60"/>
     </row>
     <row r="72" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="114" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B72" s="60" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D72" s="60">
         <v>16</v>
@@ -13487,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H72" s="93"/>
       <c r="I72" s="60"/>
@@ -13541,22 +13590,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -13567,13 +13616,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="115" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D2" s="8">
         <v>48128</v>
@@ -13587,7 +13636,7 @@
         <v>3008</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -13662,22 +13711,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -13691,10 +13740,10 @@
         <v>1000</v>
       </c>
       <c r="B2" s="111" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C2" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D2" s="111">
         <v>32</v>
@@ -13708,10 +13757,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -13720,10 +13769,10 @@
         <v>1002</v>
       </c>
       <c r="B3" s="111" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C3" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D3" s="111">
         <v>32</v>
@@ -13737,10 +13786,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -13749,10 +13798,10 @@
         <v>1004</v>
       </c>
       <c r="B4" s="111" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D4" s="111">
         <v>32</v>
@@ -13766,10 +13815,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -13778,10 +13827,10 @@
         <v>1006</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D5" s="111">
         <v>32</v>
@@ -13795,10 +13844,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -13807,10 +13856,10 @@
         <v>1008</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D6" s="111">
         <v>32</v>
@@ -13824,10 +13873,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -13836,10 +13885,10 @@
         <v>100A</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D7" s="111">
         <v>32</v>
@@ -13853,10 +13902,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -13865,10 +13914,10 @@
         <v>100C</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D8" s="111">
         <v>32</v>
@@ -13882,10 +13931,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -13894,10 +13943,10 @@
         <v>100E</v>
       </c>
       <c r="B9" s="111" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D9" s="111">
         <v>32</v>
@@ -13911,10 +13960,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -13923,10 +13972,10 @@
         <v>1010</v>
       </c>
       <c r="B10" s="111" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C10" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D10" s="111">
         <v>32</v>
@@ -13940,10 +13989,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -13952,10 +14001,10 @@
         <v>1012</v>
       </c>
       <c r="B11" s="111" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C11" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D11" s="111">
         <v>32</v>
@@ -13969,10 +14018,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -13981,10 +14030,10 @@
         <v>1014</v>
       </c>
       <c r="B12" s="111" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C12" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D12" s="111">
         <v>32</v>
@@ -13998,10 +14047,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -14010,10 +14059,10 @@
         <v>1016</v>
       </c>
       <c r="B13" s="111" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C13" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D13" s="111">
         <v>32</v>
@@ -14027,10 +14076,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -14039,10 +14088,10 @@
         <v>1018</v>
       </c>
       <c r="B14" s="111" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C14" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D14" s="111">
         <v>32</v>
@@ -14056,10 +14105,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -14068,10 +14117,10 @@
         <v>101A</v>
       </c>
       <c r="B15" s="111" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C15" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D15" s="111">
         <v>32</v>
@@ -14085,10 +14134,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -14097,10 +14146,10 @@
         <v>101C</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C16" s="118" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D16" s="111">
         <v>32</v>
@@ -14114,10 +14163,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -14126,10 +14175,10 @@
         <v>101E</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D17" s="59">
         <v>32</v>
@@ -14143,10 +14192,10 @@
         <v>2</v>
       </c>
       <c r="G17" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -14155,10 +14204,10 @@
         <v>1020</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D18" s="59">
         <v>32</v>
@@ -14172,10 +14221,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -14184,10 +14233,10 @@
         <v>1022</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C19" s="96" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D19" s="59">
         <v>32</v>
@@ -14201,10 +14250,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -14213,10 +14262,10 @@
         <v>1024</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C20" s="96" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D20" s="59">
         <v>32</v>
@@ -14230,10 +14279,10 @@
         <v>2</v>
       </c>
       <c r="G20" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -14242,10 +14291,10 @@
         <v>1026</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C21" s="96" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D21" s="59">
         <v>32</v>
@@ -14259,10 +14308,10 @@
         <v>2</v>
       </c>
       <c r="G21" s="111" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14271,10 +14320,10 @@
         <v>1028</v>
       </c>
       <c r="B22" s="101" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C22" s="97" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D22" s="101">
         <v>1920</v>
@@ -14291,7 +14340,7 @@
         <v>25</v>
       </c>
       <c r="H22" s="66" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -14300,10 +14349,10 @@
         <v>10A0</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D23" s="51">
         <v>384</v>
@@ -14317,10 +14366,10 @@
         <v>24</v>
       </c>
       <c r="G23" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -14329,10 +14378,10 @@
         <v>10B8</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C24" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D24" s="59">
         <v>384</v>
@@ -14346,10 +14395,10 @@
         <v>24</v>
       </c>
       <c r="G24" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -14358,10 +14407,10 @@
         <v>10D0</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C25" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D25" s="59">
         <v>384</v>
@@ -14375,10 +14424,10 @@
         <v>24</v>
       </c>
       <c r="G25" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -14387,10 +14436,10 @@
         <v>10E8</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C26" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D26" s="59">
         <v>384</v>
@@ -14404,10 +14453,10 @@
         <v>24</v>
       </c>
       <c r="G26" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -14416,10 +14465,10 @@
         <v>1100</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D27" s="59">
         <v>384</v>
@@ -14433,10 +14482,10 @@
         <v>24</v>
       </c>
       <c r="G27" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -14445,10 +14494,10 @@
         <v>1118</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C28" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D28" s="59">
         <v>384</v>
@@ -14462,10 +14511,10 @@
         <v>24</v>
       </c>
       <c r="G28" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -14474,10 +14523,10 @@
         <v>1130</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C29" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D29" s="59">
         <v>384</v>
@@ -14491,10 +14540,10 @@
         <v>24</v>
       </c>
       <c r="G29" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -14503,10 +14552,10 @@
         <v>1148</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C30" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D30" s="59">
         <v>384</v>
@@ -14520,10 +14569,10 @@
         <v>24</v>
       </c>
       <c r="G30" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -14532,10 +14581,10 @@
         <v>1160</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C31" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D31" s="59">
         <v>384</v>
@@ -14549,10 +14598,10 @@
         <v>24</v>
       </c>
       <c r="G31" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -14561,10 +14610,10 @@
         <v>1178</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C32" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D32" s="59">
         <v>384</v>
@@ -14578,10 +14627,10 @@
         <v>24</v>
       </c>
       <c r="G32" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -14590,10 +14639,10 @@
         <v>1190</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C33" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D33" s="59">
         <v>384</v>
@@ -14607,10 +14656,10 @@
         <v>24</v>
       </c>
       <c r="G33" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -14619,10 +14668,10 @@
         <v>11A8</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D34" s="59">
         <v>384</v>
@@ -14636,10 +14685,10 @@
         <v>24</v>
       </c>
       <c r="G34" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -14648,10 +14697,10 @@
         <v>11C0</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D35" s="59">
         <v>384</v>
@@ -14665,10 +14714,10 @@
         <v>24</v>
       </c>
       <c r="G35" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -14677,10 +14726,10 @@
         <v>11D8</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C36" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D36" s="59">
         <v>384</v>
@@ -14694,10 +14743,10 @@
         <v>24</v>
       </c>
       <c r="G36" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -14706,10 +14755,10 @@
         <v>11F0</v>
       </c>
       <c r="B37" s="59" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C37" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D37" s="59">
         <v>384</v>
@@ -14723,10 +14772,10 @@
         <v>24</v>
       </c>
       <c r="G37" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H37" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -14735,10 +14784,10 @@
         <v>1208</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C38" s="96" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D38" s="59">
         <v>384</v>
@@ -14752,10 +14801,10 @@
         <v>24</v>
       </c>
       <c r="G38" s="111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -14764,10 +14813,10 @@
         <v>1220</v>
       </c>
       <c r="B39" s="59" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C39" s="96" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D39" s="59">
         <v>256</v>
@@ -14781,10 +14830,10 @@
         <v>16</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="H39" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -14793,10 +14842,10 @@
         <v>1230</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D40" s="59">
         <v>256</v>
@@ -14810,10 +14859,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="59" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -14822,10 +14871,10 @@
         <v>1240</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C41" s="96" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D41" s="59">
         <v>256</v>
@@ -14839,10 +14888,10 @@
         <v>16</v>
       </c>
       <c r="G41" s="59" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="H41" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -14851,10 +14900,10 @@
         <v>1250</v>
       </c>
       <c r="B42" s="59" t="s">
+        <v>587</v>
+      </c>
+      <c r="C42" s="96" t="s">
         <v>590</v>
-      </c>
-      <c r="C42" s="96" t="s">
-        <v>593</v>
       </c>
       <c r="D42" s="59">
         <v>256</v>
@@ -14868,10 +14917,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14883,7 +14932,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="96" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D43" s="59">
         <v>39424</v>
@@ -14900,7 +14949,7 @@
         <v>25</v>
       </c>
       <c r="H43" s="59" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14951,22 +15000,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E1" s="113" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F1" s="113" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -14977,10 +15026,10 @@
     </row>
     <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C2" s="16">
         <v>0</v>
@@ -14997,10 +15046,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15009,7 +15058,7 @@
         <v>1C01</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C3" s="16">
         <v>0</v>
@@ -15026,10 +15075,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15038,10 +15087,10 @@
         <v>1C02</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D4" s="16">
         <v>256</v>
@@ -15055,10 +15104,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15067,10 +15116,10 @@
         <v>1C12</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D5" s="18">
         <v>384</v>
@@ -15084,10 +15133,10 @@
         <v>24</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="158.25" x14ac:dyDescent="0.25">
@@ -15096,10 +15145,10 @@
         <v>1C2A</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D6" s="18">
         <v>768</v>
@@ -15113,10 +15162,10 @@
         <v>48</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15125,10 +15174,10 @@
         <v>1C5A</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D7" s="18">
         <v>128</v>
@@ -15142,10 +15191,10 @@
         <v>8</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
@@ -15154,10 +15203,10 @@
         <v>1C62</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D8" s="18">
         <v>8192</v>
@@ -15171,10 +15220,10 @@
         <v>512</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>677</v>
+        <v>710</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -15183,10 +15232,10 @@
         <v>1E62</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D9" s="18">
         <v>768</v>
@@ -15200,10 +15249,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -15215,7 +15264,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="118" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D10" s="21">
         <v>3808</v>
@@ -15229,7 +15278,7 @@
         <v>238</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H10" s="21"/>
     </row>
@@ -15281,10 +15330,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -15295,34 +15344,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB031FF8E1109D43B2BDF0F43F684A4E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b896ebdbfa452e7a07541eac816e2062">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94916c3f-a887-466e-9071-419f2f5fc067" xmlns:ns3="0358a91d-8923-4300-9035-92feb74d70aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="556acc82b7336cf142ff4903a3ab7ecb" ns2:_="" ns3:_="">
     <xsd:import namespace="94916c3f-a887-466e-9071-419f2f5fc067"/>
@@ -15577,10 +15598,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
+    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15603,20 +15663,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
-    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
+++ b/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sdk\ast2700\OTP\memory\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sdk\ast2700\OTP\memory\release\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A973C1CC-7133-4C88-AF1F-3DA5E22E17E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27881C35-FA1F-4CDE-A85C-DC5AAFD23A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
+    <workbookView xWindow="30420" yWindow="555" windowWidth="26025" windowHeight="14775" activeTab="5" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -868,9 +868,6 @@
   </si>
   <si>
     <t>UartDbgSel</t>
-  </si>
-  <si>
-    <t>Selection of IO for Uart Debug</t>
   </si>
   <si>
     <t>Uart debug IO pin selection.</t>
@@ -1479,10 +1476,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>175: 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Register</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2723,10 +2716,6 @@
     <t>Note: This bit must be set ofgether with OTPSTRAP[18].</t>
   </si>
   <si>
-    <t>boot sofrage ABR enable
-0: disable 1: enable</t>
-  </si>
-  <si>
     <t>This bit is used of enabled ABR machenism.</t>
   </si>
   <si>
@@ -2900,13 +2889,6 @@
   </si>
   <si>
     <t>Caliptra Owner public key hash retire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Disable OTP Memory Facofry Test Mode
-0: enable
-1: disable
-of prevent security issue of OTP memory. Disabled BIST mode is recommended.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2967,6 +2949,27 @@
   </si>
   <si>
     <t>SoC FMC hardware SVN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47: 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disable OTP Memory Factory Test Mode
+0: enable
+1: disable
+of prevent security issue of OTP memory. Disabled BIST mode is recommended.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selection of IO for Uart Debug
+0: IO12 1: IO0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boot storage ABR enable
+0: disable 1: enable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4531,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4663,7 +4666,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="128" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B9" s="120" t="str">
         <f t="shared" si="5"/>
@@ -4849,22 +4852,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -4875,13 +4878,13 @@
     </row>
     <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C2" s="124" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D2" s="18">
         <v>512</v>
@@ -4895,7 +4898,7 @@
         <v>32</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H2" s="18"/>
     </row>
@@ -4905,10 +4908,10 @@
         <v>1FA0</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C3" s="124" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D3" s="18">
         <v>256</v>
@@ -4922,10 +4925,10 @@
         <v>16</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -4934,10 +4937,10 @@
         <v>1FB0</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D4" s="18">
         <v>384</v>
@@ -4951,10 +4954,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -4963,10 +4966,10 @@
         <v>1FC8</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="124" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D5" s="18">
         <v>256</v>
@@ -4980,10 +4983,10 @@
         <v>16</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4992,10 +4995,10 @@
         <v>1FD8</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6" s="124" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D6" s="18">
         <v>256</v>
@@ -5009,10 +5012,10 @@
         <v>16</v>
       </c>
       <c r="G6" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>327</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5021,10 +5024,10 @@
         <v>1FE8</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C7" s="124" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D7" s="18">
         <v>384</v>
@@ -5048,7 +5051,7 @@
         <v>2000</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="58">
@@ -5112,22 +5115,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5144,7 +5147,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D2" s="8">
         <v>15872</v>
@@ -5158,7 +5161,7 @@
         <v>992</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -5234,22 +5237,22 @@
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5275,7 +5278,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D2" s="8">
         <v>16</v>
@@ -5302,7 +5305,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D3" s="16">
         <v>16</v>
@@ -5329,7 +5332,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D4" s="16">
         <v>16</v>
@@ -5353,10 +5356,10 @@
         <v>3E3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D5" s="16">
         <v>16</v>
@@ -5370,7 +5373,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>27</v>
@@ -5385,7 +5388,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D6" s="16">
         <v>64</v>
@@ -5399,7 +5402,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>29</v>
@@ -5414,7 +5417,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D7" s="16">
         <v>32</v>
@@ -5443,7 +5446,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D8" s="16">
         <v>128</v>
@@ -5472,7 +5475,7 @@
         <v>34</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D9" s="16">
         <v>4</v>
@@ -5501,7 +5504,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" s="16">
         <v>32</v>
@@ -5527,10 +5530,10 @@
         <v>3F5</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C11" s="96" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D11" s="16">
         <v>128</v>
@@ -5544,7 +5547,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="H11" s="20" t="s">
         <v>29</v>
@@ -5559,18 +5562,18 @@
         <v>25</v>
       </c>
       <c r="C12" s="63" t="s">
-        <v>342</v>
+        <v>715</v>
       </c>
       <c r="D12" s="24">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="E12" s="24">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F12" s="24">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G12" s="24" t="s">
         <v>25</v>
@@ -5582,7 +5585,7 @@
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f t="shared" si="2"/>
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>22</v>
@@ -5590,15 +5593,15 @@
       <c r="C13" s="61"/>
       <c r="D13" s="12">
         <f>SUM(D2:D12)</f>
-        <v>628</v>
+        <v>500</v>
       </c>
       <c r="E13" s="12">
         <f>SUM(E2:E12)</f>
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F13" s="12">
         <f>SUM(F2:F12)</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="14"/>
@@ -5606,7 +5609,7 @@
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="str">
         <f>DEC2HEX(F14)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>23</v>
@@ -5614,15 +5617,15 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8">
         <f>F13*16</f>
-        <v>640</v>
+        <v>512</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" ref="E14" si="8">QUOTIENT(D14+7,8)</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" ref="F14" si="9">QUOTIENT(E14+1,2)</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
@@ -5652,22 +5655,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -5676,7 +5679,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5704,10 +5707,10 @@
         <v>40</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5735,10 +5738,10 @@
         <v>42</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I3" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -5763,13 +5766,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I4" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5797,10 +5800,10 @@
         <v>45</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I5" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -5828,10 +5831,10 @@
         <v>47</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I6" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5859,10 +5862,10 @@
         <v>49</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I7" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -5887,13 +5890,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="71" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I8" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5921,10 +5924,10 @@
         <v>25</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I9" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5952,10 +5955,10 @@
         <v>52</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I10" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -5983,10 +5986,10 @@
         <v>54</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I11" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -6014,10 +6017,10 @@
         <v>56</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I12" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6045,10 +6048,10 @@
         <v>58</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I13" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6076,10 +6079,10 @@
         <v>60</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I14" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6107,10 +6110,10 @@
         <v>62</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I15" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6138,10 +6141,10 @@
         <v>64</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I16" s="74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6169,10 +6172,10 @@
         <v>66</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I17" s="94" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6184,7 +6187,7 @@
         <v>67</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D18" s="68">
         <v>16</v>
@@ -6201,10 +6204,10 @@
         <v>68</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -6213,7 +6216,7 @@
         <v>402</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C19" s="64">
         <v>15</v>
@@ -6230,11 +6233,11 @@
         <v>1</v>
       </c>
       <c r="G19" s="78" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="H19" s="78"/>
       <c r="I19" s="15" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -6242,7 +6245,7 @@
         <v>402</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C20" s="64">
         <v>14</v>
@@ -6259,11 +6262,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="H20" s="34"/>
       <c r="I20" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6292,7 +6295,7 @@
       </c>
       <c r="H21" s="59"/>
       <c r="I21" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -6321,7 +6324,7 @@
       </c>
       <c r="H22" s="59"/>
       <c r="I22" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -6350,7 +6353,7 @@
       </c>
       <c r="H23" s="59"/>
       <c r="I23" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -6379,7 +6382,7 @@
       </c>
       <c r="H24" s="59"/>
       <c r="I24" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -6390,7 +6393,7 @@
         <v>71</v>
       </c>
       <c r="C25" s="63" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D25" s="8">
         <v>2</v>
@@ -6404,13 +6407,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="79" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -6421,7 +6424,7 @@
         <v>72</v>
       </c>
       <c r="C26" s="63" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D26" s="8">
         <v>2</v>
@@ -6438,10 +6441,10 @@
         <v>73</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -6466,13 +6469,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="79" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -6500,10 +6503,10 @@
         <v>76</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -6531,10 +6534,10 @@
         <v>78</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -6563,7 +6566,7 @@
       </c>
       <c r="H30" s="59"/>
       <c r="I30" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -6592,7 +6595,7 @@
       </c>
       <c r="H31" s="59"/>
       <c r="I31" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6617,13 +6620,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H32" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6634,7 +6637,7 @@
         <v>80</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D33" s="68">
         <v>16</v>
@@ -6652,7 +6655,7 @@
       </c>
       <c r="H33" s="50"/>
       <c r="I33" s="42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -6663,7 +6666,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D34" s="8">
         <v>5</v>
@@ -6677,11 +6680,11 @@
         <v>1</v>
       </c>
       <c r="G34" s="86" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H34" s="51"/>
       <c r="I34" s="15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6692,7 +6695,7 @@
         <v>82</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D35" s="16">
         <v>10</v>
@@ -6709,10 +6712,10 @@
         <v>83</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6737,13 +6740,13 @@
         <v>1</v>
       </c>
       <c r="G36" s="99" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="H36" s="60" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -6754,7 +6757,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D37" s="8">
         <v>6</v>
@@ -6768,11 +6771,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="86" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H37" s="51"/>
       <c r="I37" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6783,7 +6786,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="97" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D38" s="66">
         <v>10</v>
@@ -6797,13 +6800,13 @@
         <v>1</v>
       </c>
       <c r="G38" s="99" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H38" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -6814,7 +6817,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D39" s="8">
         <v>5</v>
@@ -6832,7 +6835,7 @@
       </c>
       <c r="H39" s="51"/>
       <c r="I39" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -6843,7 +6846,7 @@
         <v>86</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D40" s="16">
         <v>10</v>
@@ -6860,10 +6863,10 @@
         <v>83</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6891,10 +6894,10 @@
         <v>88</v>
       </c>
       <c r="H41" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I41" s="41" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -6905,7 +6908,7 @@
         <v>26</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D42" s="8">
         <v>6</v>
@@ -6923,7 +6926,7 @@
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -6934,7 +6937,7 @@
         <v>89</v>
       </c>
       <c r="C43" s="97" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D43" s="66">
         <v>10</v>
@@ -6948,13 +6951,13 @@
         <v>1</v>
       </c>
       <c r="G43" s="99" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H43" s="101" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I43" s="41" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6965,7 +6968,7 @@
         <v>26</v>
       </c>
       <c r="C44" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D44" s="68">
         <v>16</v>
@@ -6983,7 +6986,7 @@
       </c>
       <c r="H44" s="50"/>
       <c r="I44" s="42" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -6991,7 +6994,7 @@
         <v>409</v>
       </c>
       <c r="B45" s="83" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C45" s="64">
         <v>15</v>
@@ -7008,13 +7011,13 @@
         <v>1</v>
       </c>
       <c r="G45" s="88" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -7022,7 +7025,7 @@
         <v>409</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C46" s="100">
         <v>14</v>
@@ -7039,13 +7042,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="H46" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -7053,7 +7056,7 @@
         <v>409</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C47" s="100">
         <v>13</v>
@@ -7070,13 +7073,13 @@
         <v>1</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -7084,7 +7087,7 @@
         <v>409</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C48" s="100">
         <v>12</v>
@@ -7101,13 +7104,13 @@
         <v>1</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H48" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -7115,7 +7118,7 @@
         <v>409</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C49" s="100">
         <v>11</v>
@@ -7132,13 +7135,13 @@
         <v>1</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -7146,7 +7149,7 @@
         <v>409</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C50" s="100">
         <v>10</v>
@@ -7163,13 +7166,13 @@
         <v>1</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H50" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -7177,7 +7180,7 @@
         <v>409</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C51" s="100">
         <v>9</v>
@@ -7194,13 +7197,13 @@
         <v>1</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -7208,7 +7211,7 @@
         <v>409</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C52" s="100">
         <v>8</v>
@@ -7225,13 +7228,13 @@
         <v>1</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -7239,7 +7242,7 @@
         <v>409</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C53" s="100">
         <v>7</v>
@@ -7256,13 +7259,13 @@
         <v>1</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -7270,7 +7273,7 @@
         <v>409</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C54" s="100">
         <v>6</v>
@@ -7287,13 +7290,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H54" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -7301,7 +7304,7 @@
         <v>409</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C55" s="100">
         <v>5</v>
@@ -7318,13 +7321,13 @@
         <v>1</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I55" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -7332,7 +7335,7 @@
         <v>409</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C56" s="100">
         <v>4</v>
@@ -7349,13 +7352,13 @@
         <v>1</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H56" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -7363,7 +7366,7 @@
         <v>409</v>
       </c>
       <c r="B57" s="29" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C57" s="100">
         <v>3</v>
@@ -7380,13 +7383,13 @@
         <v>1</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -7394,7 +7397,7 @@
         <v>409</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C58" s="100">
         <v>2</v>
@@ -7411,13 +7414,13 @@
         <v>1</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H58" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -7425,7 +7428,7 @@
         <v>409</v>
       </c>
       <c r="B59" s="29" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C59" s="100">
         <v>1</v>
@@ -7442,13 +7445,13 @@
         <v>1</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -7456,7 +7459,7 @@
         <v>409</v>
       </c>
       <c r="B60" s="84" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C60" s="64">
         <v>0</v>
@@ -7473,24 +7476,24 @@
         <v>1</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H60" s="101" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="151" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B61" s="152" t="s">
         <v>26</v>
       </c>
       <c r="C61" s="102" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D61" s="103">
         <v>8</v>
@@ -7507,18 +7510,18 @@
         <v>25</v>
       </c>
       <c r="H61" s="154" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I61" s="155" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C62" s="64">
         <v>7</v>
@@ -7535,21 +7538,21 @@
         <v>1</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H62" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C63" s="64">
         <v>6</v>
@@ -7566,21 +7569,21 @@
         <v>1</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H63" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C64" s="64">
         <v>5</v>
@@ -7597,21 +7600,21 @@
         <v>1</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H64" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C65" s="64">
         <v>4</v>
@@ -7628,21 +7631,21 @@
         <v>1</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H65" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C66" s="64">
         <v>3</v>
@@ -7659,21 +7662,21 @@
         <v>1</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H66" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C67" s="64">
         <v>2</v>
@@ -7690,21 +7693,21 @@
         <v>1</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H67" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="120" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C68" s="64">
         <v>1</v>
@@ -7721,21 +7724,21 @@
         <v>1</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H68" s="59" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="122" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B69" s="153" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C69" s="95">
         <v>0</v>
@@ -7752,21 +7755,21 @@
         <v>1</v>
       </c>
       <c r="G69" s="46" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H69" s="101" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I69" s="46" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A70" s="142" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B70" s="43" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C70" s="64">
         <v>15</v>
@@ -7783,18 +7786,18 @@
         <v>1</v>
       </c>
       <c r="G70" s="44" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="120" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B71" s="77" t="s">
         <v>90</v>
@@ -7817,15 +7820,15 @@
         <v>91</v>
       </c>
       <c r="H71" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="120" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B72" s="77" t="s">
         <v>92</v>
@@ -7848,15 +7851,15 @@
         <v>93</v>
       </c>
       <c r="H72" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I72" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="120" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B73" s="77" t="s">
         <v>26</v>
@@ -7880,18 +7883,18 @@
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="122" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B74" s="82" t="s">
         <v>94</v>
       </c>
       <c r="C74" s="97" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D74" s="66">
         <v>12</v>
@@ -7908,21 +7911,21 @@
         <v>95</v>
       </c>
       <c r="H74" s="101" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I74" s="41" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="150" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B75" s="85" t="s">
         <v>96</v>
       </c>
       <c r="C75" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D75" s="68">
         <v>16</v>
@@ -7939,18 +7942,18 @@
         <v>97</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I75" s="42" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A76" s="142" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B76" s="43" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C76" s="64">
         <v>15</v>
@@ -7967,18 +7970,18 @@
         <v>1</v>
       </c>
       <c r="G76" s="88" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H76" s="51" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I76" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="120" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B77" s="77" t="s">
         <v>98</v>
@@ -8001,15 +8004,15 @@
         <v>99</v>
       </c>
       <c r="H77" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="120" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B78" s="77" t="s">
         <v>100</v>
@@ -8032,15 +8035,15 @@
         <v>101</v>
       </c>
       <c r="H78" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I78" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="120" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B79" s="77" t="s">
         <v>26</v>
@@ -8064,18 +8067,18 @@
       </c>
       <c r="H79" s="59"/>
       <c r="I79" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="122" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B80" s="82" t="s">
         <v>102</v>
       </c>
       <c r="C80" s="97" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D80" s="66">
         <v>12</v>
@@ -8092,21 +8095,21 @@
         <v>103</v>
       </c>
       <c r="H80" s="101" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I80" s="41" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="150" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B81" s="85" t="s">
         <v>104</v>
       </c>
       <c r="C81" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D81" s="68">
         <v>16</v>
@@ -8123,21 +8126,21 @@
         <v>105</v>
       </c>
       <c r="H81" s="50" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="142" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C82" s="63" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D82" s="8">
         <v>8</v>
@@ -8154,21 +8157,21 @@
         <v>107</v>
       </c>
       <c r="H82" s="51" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I82" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="120" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B83" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C83" s="96" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D83" s="16">
         <v>3</v>
@@ -8186,12 +8189,12 @@
       </c>
       <c r="H83" s="59"/>
       <c r="I83" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="120" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B84" s="29" t="s">
         <v>108</v>
@@ -8214,21 +8217,21 @@
         <v>109</v>
       </c>
       <c r="H84" s="59" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I84" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="122" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B85" s="37" t="s">
         <v>110</v>
       </c>
       <c r="C85" s="97" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D85" s="66">
         <v>4</v>
@@ -8245,10 +8248,10 @@
         <v>111</v>
       </c>
       <c r="H85" s="101" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I85" s="46" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -8259,7 +8262,7 @@
         <v>26</v>
       </c>
       <c r="C86" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D86" s="68">
         <v>16</v>
@@ -8277,7 +8280,7 @@
       </c>
       <c r="H86" s="50"/>
       <c r="I86" s="42" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8305,10 +8308,10 @@
         <v>113</v>
       </c>
       <c r="H87" s="51" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I87" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -8333,13 +8336,13 @@
         <v>1</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H88" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8350,7 +8353,7 @@
         <v>115</v>
       </c>
       <c r="C89" s="96" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D89" s="16">
         <v>2</v>
@@ -8367,10 +8370,10 @@
         <v>116</v>
       </c>
       <c r="H89" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -8395,13 +8398,13 @@
         <v>1</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H90" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8412,7 +8415,7 @@
         <v>118</v>
       </c>
       <c r="C91" s="96" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D91" s="16">
         <v>2</v>
@@ -8429,10 +8432,10 @@
         <v>119</v>
       </c>
       <c r="H91" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I91" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -8457,13 +8460,13 @@
         <v>1</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H92" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I92" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8474,7 +8477,7 @@
         <v>121</v>
       </c>
       <c r="C93" s="96" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D93" s="16">
         <v>2</v>
@@ -8491,10 +8494,10 @@
         <v>122</v>
       </c>
       <c r="H93" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I93" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -8519,13 +8522,13 @@
         <v>1</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H94" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8536,7 +8539,7 @@
         <v>124</v>
       </c>
       <c r="C95" s="96" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D95" s="16">
         <v>2</v>
@@ -8553,10 +8556,10 @@
         <v>125</v>
       </c>
       <c r="H95" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I95" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -8581,13 +8584,13 @@
         <v>1</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H96" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I96" s="15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -8598,7 +8601,7 @@
         <v>127</v>
       </c>
       <c r="C97" s="97" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D97" s="66">
         <v>2</v>
@@ -8615,10 +8618,10 @@
         <v>128</v>
       </c>
       <c r="H97" s="101" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I97" s="46" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8629,7 +8632,7 @@
         <v>129</v>
       </c>
       <c r="C98" s="63" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D98" s="8">
         <v>2</v>
@@ -8646,10 +8649,10 @@
         <v>130</v>
       </c>
       <c r="H98" s="51" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -8674,13 +8677,13 @@
         <v>1</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H99" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I99" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8691,7 +8694,7 @@
         <v>132</v>
       </c>
       <c r="C100" s="96" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D100" s="16">
         <v>2</v>
@@ -8708,10 +8711,10 @@
         <v>133</v>
       </c>
       <c r="H100" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I100" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -8736,13 +8739,13 @@
         <v>1</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H101" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I101" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8753,7 +8756,7 @@
         <v>135</v>
       </c>
       <c r="C102" s="96" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D102" s="16">
         <v>2</v>
@@ -8770,10 +8773,10 @@
         <v>136</v>
       </c>
       <c r="H102" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I102" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -8798,13 +8801,13 @@
         <v>1</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H103" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I103" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8815,7 +8818,7 @@
         <v>138</v>
       </c>
       <c r="C104" s="96" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D104" s="16">
         <v>2</v>
@@ -8832,10 +8835,10 @@
         <v>139</v>
       </c>
       <c r="H104" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I104" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -8860,13 +8863,13 @@
         <v>1</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H105" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I105" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -8877,7 +8880,7 @@
         <v>141</v>
       </c>
       <c r="C106" s="96" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D106" s="16">
         <v>2</v>
@@ -8894,10 +8897,10 @@
         <v>142</v>
       </c>
       <c r="H106" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I106" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -8922,13 +8925,13 @@
         <v>1</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H107" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I107" s="15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -8956,10 +8959,10 @@
         <v>145</v>
       </c>
       <c r="H108" s="101" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I108" s="46" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -8970,7 +8973,7 @@
         <v>146</v>
       </c>
       <c r="C109" s="63" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D109" s="8">
         <v>3</v>
@@ -8987,10 +8990,10 @@
         <v>147</v>
       </c>
       <c r="H109" s="51" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I109" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -9001,7 +9004,7 @@
         <v>26</v>
       </c>
       <c r="C110" s="96" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D110" s="16">
         <v>3</v>
@@ -9019,7 +9022,7 @@
       </c>
       <c r="H110" s="59"/>
       <c r="I110" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -9044,13 +9047,13 @@
         <v>1</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H111" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I111" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -9078,10 +9081,10 @@
         <v>150</v>
       </c>
       <c r="H112" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I112" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -9106,13 +9109,13 @@
         <v>1</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H113" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I113" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -9137,13 +9140,13 @@
         <v>1</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H114" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I114" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -9154,7 +9157,7 @@
         <v>153</v>
       </c>
       <c r="C115" s="96" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D115" s="16">
         <v>2</v>
@@ -9171,10 +9174,10 @@
         <v>154</v>
       </c>
       <c r="H115" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -9199,13 +9202,13 @@
         <v>1</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H116" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I116" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -9216,7 +9219,7 @@
         <v>156</v>
       </c>
       <c r="C117" s="96" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D117" s="16">
         <v>2</v>
@@ -9233,10 +9236,10 @@
         <v>157</v>
       </c>
       <c r="H117" s="59" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I117" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9261,13 +9264,13 @@
         <v>1</v>
       </c>
       <c r="G118" s="46" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H118" s="101" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I118" s="46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -9275,7 +9278,7 @@
         <v>414</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C119" s="64">
         <v>15</v>
@@ -9292,13 +9295,13 @@
         <v>1</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="H119" s="51" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I119" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -9326,10 +9329,10 @@
         <v>160</v>
       </c>
       <c r="H120" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I120" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -9357,10 +9360,10 @@
         <v>162</v>
       </c>
       <c r="H121" s="59" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I121" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -9389,7 +9392,7 @@
       </c>
       <c r="H122" s="59"/>
       <c r="I122" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9400,7 +9403,7 @@
         <v>163</v>
       </c>
       <c r="C123" s="97" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D123" s="66">
         <v>12</v>
@@ -9417,10 +9420,10 @@
         <v>164</v>
       </c>
       <c r="H123" s="101" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I123" s="46" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9431,7 +9434,7 @@
         <v>165</v>
       </c>
       <c r="C124" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D124" s="68">
         <v>16</v>
@@ -9448,10 +9451,10 @@
         <v>166</v>
       </c>
       <c r="H124" s="50" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I124" s="42" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9459,10 +9462,10 @@
         <v>416</v>
       </c>
       <c r="B125" s="40" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C125" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D125" s="68">
         <v>16</v>
@@ -9476,13 +9479,13 @@
         <v>1</v>
       </c>
       <c r="G125" s="42" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H125" s="50" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I125" s="42" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -9493,7 +9496,7 @@
         <v>26</v>
       </c>
       <c r="C126" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D126" s="68">
         <v>16</v>
@@ -9510,10 +9513,10 @@
         <v>26</v>
       </c>
       <c r="H126" s="50" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I126" s="42" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -9524,7 +9527,7 @@
         <v>26</v>
       </c>
       <c r="C127" s="63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D127" s="8">
         <v>5</v>
@@ -9542,7 +9545,7 @@
       </c>
       <c r="H127" s="51"/>
       <c r="I127" s="15" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -9553,7 +9556,7 @@
         <v>167</v>
       </c>
       <c r="C128" s="96" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D128" s="16">
         <v>10</v>
@@ -9570,10 +9573,10 @@
         <v>83</v>
       </c>
       <c r="H128" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I128" s="15" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -9601,10 +9604,10 @@
         <v>169</v>
       </c>
       <c r="H129" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I129" s="46" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -9615,7 +9618,7 @@
         <v>26</v>
       </c>
       <c r="C130" s="63" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D130" s="8">
         <v>6</v>
@@ -9633,7 +9636,7 @@
       </c>
       <c r="H130" s="51"/>
       <c r="I130" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -9644,7 +9647,7 @@
         <v>170</v>
       </c>
       <c r="C131" s="97" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D131" s="66">
         <v>10</v>
@@ -9658,24 +9661,24 @@
         <v>1</v>
       </c>
       <c r="G131" s="46" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H131" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I131" s="46" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="142" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C132" s="63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D132" s="8">
         <v>5</v>
@@ -9693,18 +9696,18 @@
       </c>
       <c r="H132" s="51"/>
       <c r="I132" s="15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" s="120" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B133" s="29" t="s">
         <v>171</v>
       </c>
       <c r="C133" s="96" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D133" s="16">
         <v>10</v>
@@ -9721,15 +9724,15 @@
         <v>83</v>
       </c>
       <c r="H133" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I133" s="15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="122" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B134" s="37" t="s">
         <v>172</v>
@@ -9752,21 +9755,21 @@
         <v>173</v>
       </c>
       <c r="H134" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I134" s="46" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="142" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C135" s="63" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D135" s="8">
         <v>6</v>
@@ -9784,18 +9787,18 @@
       </c>
       <c r="H135" s="51"/>
       <c r="I135" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="122" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B136" s="37" t="s">
         <v>174</v>
       </c>
       <c r="C136" s="97" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D136" s="66">
         <v>10</v>
@@ -9809,24 +9812,24 @@
         <v>1</v>
       </c>
       <c r="G136" s="46" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H136" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I136" s="46" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="142" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C137" s="63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D137" s="8">
         <v>5</v>
@@ -9844,18 +9847,18 @@
       </c>
       <c r="H137" s="51"/>
       <c r="I137" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B138" s="29" t="s">
         <v>175</v>
       </c>
       <c r="C138" s="96" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D138" s="16">
         <v>10</v>
@@ -9872,15 +9875,15 @@
         <v>83</v>
       </c>
       <c r="H138" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I138" s="15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="122" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B139" s="37" t="s">
         <v>176</v>
@@ -9903,21 +9906,21 @@
         <v>177</v>
       </c>
       <c r="H139" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I139" s="46" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="142" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C140" s="63" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D140" s="8">
         <v>6</v>
@@ -9935,18 +9938,18 @@
       </c>
       <c r="H140" s="51"/>
       <c r="I140" s="15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="122" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B141" s="37" t="s">
         <v>178</v>
       </c>
       <c r="C141" s="97" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D141" s="66">
         <v>10</v>
@@ -9960,24 +9963,24 @@
         <v>1</v>
       </c>
       <c r="G141" s="46" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H141" s="101" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I141" s="46" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="150" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B142" s="105" t="s">
         <v>26</v>
       </c>
       <c r="C142" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D142" s="68">
         <v>16</v>
@@ -9995,18 +9998,18 @@
       </c>
       <c r="H142" s="50"/>
       <c r="I142" s="42" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="114" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B143" s="45" t="s">
         <v>26</v>
       </c>
       <c r="C143" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D143" s="93">
         <v>16</v>
@@ -10024,7 +10027,7 @@
       </c>
       <c r="H143" s="60"/>
       <c r="I143" s="41" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -10076,22 +10079,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -10100,7 +10103,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10108,10 +10111,10 @@
         <v>420</v>
       </c>
       <c r="B2" s="144" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C2" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D2" s="144">
         <v>16</v>
@@ -10125,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="144" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H2" s="144"/>
       <c r="I2" s="144"/>
@@ -10135,10 +10138,10 @@
         <v>421</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C3" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D3" s="144">
         <v>16</v>
@@ -10152,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="144" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H3" s="144"/>
       <c r="I3" s="144"/>
@@ -10162,7 +10165,7 @@
         <v>422</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C4" s="51">
         <v>0</v>
@@ -10183,7 +10186,7 @@
       </c>
       <c r="H4" s="51"/>
       <c r="I4" s="51" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -10208,13 +10211,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10225,7 +10228,7 @@
         <v>180</v>
       </c>
       <c r="C6" s="96" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D6" s="59">
         <v>2</v>
@@ -10239,13 +10242,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10270,13 +10273,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -10287,7 +10290,7 @@
         <v>183</v>
       </c>
       <c r="C8" s="96" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D8" s="59">
         <v>2</v>
@@ -10301,13 +10304,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10332,13 +10335,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10363,13 +10366,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>186</v>
       </c>
       <c r="I10" s="59" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10377,7 +10380,7 @@
         <v>422</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="59">
         <v>9</v>
@@ -10394,13 +10397,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>187</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10425,13 +10428,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>189</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10456,13 +10459,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>189</v>
       </c>
       <c r="I13" s="59" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10487,13 +10490,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10518,13 +10521,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>181</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -10553,7 +10556,7 @@
       </c>
       <c r="H16" s="59"/>
       <c r="I16" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10582,7 +10585,7 @@
       </c>
       <c r="H17" s="101"/>
       <c r="I17" s="101" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10607,13 +10610,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="I18" s="59" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10638,13 +10641,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>195</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -10669,13 +10672,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="I20" s="59" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10700,16 +10703,16 @@
         <v>1</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>199</v>
       </c>
       <c r="I21" s="59" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A22" s="59">
         <v>423</v>
       </c>
@@ -10730,14 +10733,14 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="I22" s="59" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10745,7 +10748,7 @@
         <v>423</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C23" s="59">
         <v>5</v>
@@ -10762,13 +10765,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -10776,7 +10779,7 @@
         <v>423</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="59">
         <v>6</v>
@@ -10793,13 +10796,13 @@
         <v>1</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="I24" s="59" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -10807,7 +10810,7 @@
         <v>423</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C25" s="59">
         <v>7</v>
@@ -10824,13 +10827,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="I25" s="59" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -10838,7 +10841,7 @@
         <v>423</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="59">
         <v>8</v>
@@ -10855,13 +10858,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="I26" s="59" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="120" x14ac:dyDescent="0.25">
@@ -10869,7 +10872,7 @@
         <v>423</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="59">
         <v>9</v>
@@ -10886,13 +10889,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I27" s="59" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="165" x14ac:dyDescent="0.25">
@@ -10900,7 +10903,7 @@
         <v>423</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C28" s="59">
         <v>10</v>
@@ -10917,13 +10920,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="I28" s="59" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -10931,10 +10934,10 @@
         <v>423</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="96" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D29" s="59">
         <v>2</v>
@@ -10948,13 +10951,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I29" s="59" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -10962,10 +10965,10 @@
         <v>423</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C30" s="96" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D30" s="59">
         <v>2</v>
@@ -10979,13 +10982,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -10993,7 +10996,7 @@
         <v>423</v>
       </c>
       <c r="B31" s="101" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C31" s="101">
         <v>15</v>
@@ -11010,13 +11013,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="66" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H31" s="112" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="I31" s="101" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11024,10 +11027,10 @@
         <v>424</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D32" s="144">
         <v>16</v>
@@ -11041,7 +11044,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="145" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
@@ -11051,10 +11054,10 @@
         <v>425</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D33" s="144">
         <v>16</v>
@@ -11068,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="145" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H33" s="50"/>
       <c r="I33" s="50"/>
@@ -11078,10 +11081,10 @@
         <v>426</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D34" s="144">
         <v>16</v>
@@ -11095,7 +11098,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="145" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H34" s="50"/>
       <c r="I34" s="50"/>
@@ -11105,10 +11108,10 @@
         <v>427</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D35" s="144">
         <v>16</v>
@@ -11122,7 +11125,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="145" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H35" s="50"/>
       <c r="I35" s="50"/>
@@ -11132,10 +11135,10 @@
         <v>428</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C36" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D36" s="144">
         <v>16</v>
@@ -11149,7 +11152,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="145" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H36" s="50"/>
       <c r="I36" s="50"/>
@@ -11159,10 +11162,10 @@
         <v>429</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D37" s="144">
         <v>16</v>
@@ -11176,20 +11179,20 @@
         <v>1</v>
       </c>
       <c r="G37" s="145" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H37" s="50"/>
       <c r="I37" s="50"/>
     </row>
     <row r="38" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="150" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D38" s="144">
         <v>16</v>
@@ -11203,20 +11206,20 @@
         <v>1</v>
       </c>
       <c r="G38" s="145" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H38" s="50"/>
       <c r="I38" s="50"/>
     </row>
     <row r="39" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="150" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D39" s="144">
         <v>16</v>
@@ -11230,20 +11233,20 @@
         <v>1</v>
       </c>
       <c r="G39" s="145" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H39" s="50"/>
       <c r="I39" s="50"/>
     </row>
     <row r="40" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="150" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B40" s="50" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D40" s="144">
         <v>16</v>
@@ -11257,20 +11260,20 @@
         <v>1</v>
       </c>
       <c r="G40" s="145" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H40" s="50"/>
       <c r="I40" s="50"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="150" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B41" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C41" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D41" s="144">
         <v>16</v>
@@ -11284,20 +11287,20 @@
         <v>1</v>
       </c>
       <c r="G41" s="145" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H41" s="50"/>
       <c r="I41" s="50"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="121" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B42" s="133" t="s">
+        <v>599</v>
+      </c>
+      <c r="C42" s="118" t="s">
         <v>601</v>
-      </c>
-      <c r="C42" s="118" t="s">
-        <v>603</v>
       </c>
       <c r="D42" s="133">
         <v>15</v>
@@ -11311,17 +11314,17 @@
         <v>1</v>
       </c>
       <c r="G42" s="134" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H42" s="135"/>
       <c r="I42" s="133"/>
     </row>
     <row r="43" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B43" s="136" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C43" s="136">
         <v>0</v>
@@ -11338,20 +11341,20 @@
         <v>1</v>
       </c>
       <c r="G43" s="137" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H43" s="138"/>
       <c r="I43" s="136"/>
     </row>
     <row r="44" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="114" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B44" s="130" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C44" s="96" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D44" s="130">
         <v>16</v>
@@ -11365,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="131" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H44" s="132"/>
       <c r="I44" s="130"/>
@@ -11431,22 +11434,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -11455,7 +11458,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="113" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11466,7 +11469,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="97" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D2" s="101">
         <v>16</v>
@@ -11480,11 +11483,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H2" s="66"/>
       <c r="I2" s="101" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -11492,7 +11495,7 @@
         <v>431</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" s="51">
         <v>0</v>
@@ -11509,13 +11512,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>214</v>
-      </c>
       <c r="I3" s="51" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -11540,11 +11543,11 @@
         <v>1</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="59" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11552,7 +11555,7 @@
         <v>431</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C5" s="59">
         <v>2</v>
@@ -11569,13 +11572,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I5" s="59" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -11583,7 +11586,7 @@
         <v>431</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C6" s="59">
         <v>3</v>
@@ -11600,13 +11603,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I6" s="59" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11614,7 +11617,7 @@
         <v>431</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C7" s="59">
         <v>4</v>
@@ -11631,13 +11634,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I7" s="59" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -11645,7 +11648,7 @@
         <v>431</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" s="59">
         <v>5</v>
@@ -11662,13 +11665,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11676,7 +11679,7 @@
         <v>431</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" s="59">
         <v>6</v>
@@ -11693,13 +11696,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="I9" s="59" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -11724,11 +11727,11 @@
         <v>1</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="59" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -11753,11 +11756,11 @@
         <v>1</v>
       </c>
       <c r="G11" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" s="59" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11785,10 +11788,10 @@
         <v>197</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11796,7 +11799,7 @@
         <v>431</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C13" s="107">
         <v>0.46527777777777779</v>
@@ -11813,11 +11816,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="59" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11825,7 +11828,7 @@
         <v>431</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="59">
         <v>12</v>
@@ -11842,13 +11845,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -11856,7 +11859,7 @@
         <v>431</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C15" s="59">
         <v>13</v>
@@ -11873,13 +11876,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I15" s="59" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11887,7 +11890,7 @@
         <v>431</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C16" s="59">
         <v>14</v>
@@ -11904,11 +11907,11 @@
         <v>1</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="59" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -11933,11 +11936,11 @@
         <v>1</v>
       </c>
       <c r="G17" s="101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H17" s="66"/>
       <c r="I17" s="101" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -11945,7 +11948,7 @@
         <v>432</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C18" s="51">
         <v>0</v>
@@ -11962,13 +11965,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>655</v>
+        <v>718</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I18" s="51" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
@@ -11976,7 +11979,7 @@
         <v>432</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" s="59">
         <v>1</v>
@@ -11993,13 +11996,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -12010,7 +12013,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="108" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D20" s="59">
         <v>5</v>
@@ -12024,11 +12027,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="59" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -12036,10 +12039,10 @@
         <v>432</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C21" s="108" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D21" s="59">
         <v>2</v>
@@ -12053,13 +12056,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>223</v>
-      </c>
       <c r="I21" s="59" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -12070,7 +12073,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="108" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D22" s="59">
         <v>2</v>
@@ -12084,11 +12087,11 @@
         <v>1</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="59" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="63" x14ac:dyDescent="0.25">
@@ -12096,7 +12099,7 @@
         <v>432</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" s="59">
         <v>11</v>
@@ -12113,13 +12116,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -12127,7 +12130,7 @@
         <v>432</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C24" s="59">
         <v>12</v>
@@ -12148,7 +12151,7 @@
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="59" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12156,10 +12159,10 @@
         <v>432</v>
       </c>
       <c r="B25" s="101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="109" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D25" s="101">
         <v>3</v>
@@ -12173,13 +12176,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="66" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H25" s="66" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="I25" s="101" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12187,7 +12190,7 @@
         <v>433</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26" s="51">
         <v>0</v>
@@ -12204,13 +12207,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -12221,7 +12224,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="108" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D27" s="59">
         <v>2</v>
@@ -12235,11 +12238,11 @@
         <v>1</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="59" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -12250,7 +12253,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="108" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D28" s="59">
         <v>3</v>
@@ -12264,11 +12267,11 @@
         <v>1</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="59" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12293,11 +12296,11 @@
         <v>1</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="59" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
@@ -12305,10 +12308,10 @@
         <v>433</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C30" s="108" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D30" s="59">
         <v>2</v>
@@ -12322,13 +12325,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -12336,7 +12339,7 @@
         <v>433</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C31" s="59">
         <v>9</v>
@@ -12353,13 +12356,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12367,7 +12370,7 @@
         <v>433</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C32" s="59">
         <v>10</v>
@@ -12384,11 +12387,11 @@
         <v>1</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="59" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
@@ -12396,7 +12399,7 @@
         <v>433</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C33" s="59">
         <v>11</v>
@@ -12413,13 +12416,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="126" x14ac:dyDescent="0.25">
@@ -12427,7 +12430,7 @@
         <v>433</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C34" s="59">
         <v>12</v>
@@ -12444,13 +12447,13 @@
         <v>1</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="I34" s="59" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -12458,7 +12461,7 @@
         <v>433</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C35" s="59">
         <v>13</v>
@@ -12475,13 +12478,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12492,7 +12495,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="109" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D36" s="101">
         <v>2</v>
@@ -12506,11 +12509,11 @@
         <v>1</v>
       </c>
       <c r="G36" s="101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H36" s="66"/>
       <c r="I36" s="101" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -12521,7 +12524,7 @@
         <v>26</v>
       </c>
       <c r="C37" s="110" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D37" s="51">
         <v>3</v>
@@ -12535,11 +12538,11 @@
         <v>1</v>
       </c>
       <c r="G37" s="111" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="59" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -12564,11 +12567,11 @@
         <v>1</v>
       </c>
       <c r="G38" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H38" s="16"/>
       <c r="I38" s="59" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -12579,7 +12582,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="108" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D39" s="59">
         <v>2</v>
@@ -12593,11 +12596,11 @@
         <v>1</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H39" s="16"/>
       <c r="I39" s="59" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12605,7 +12608,7 @@
         <v>434</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C40" s="59">
         <v>6</v>
@@ -12622,11 +12625,11 @@
         <v>1</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="59" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -12634,7 +12637,7 @@
         <v>434</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C41" s="59">
         <v>7</v>
@@ -12651,11 +12654,11 @@
         <v>1</v>
       </c>
       <c r="G41" s="59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H41" s="16"/>
       <c r="I41" s="59" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -12663,7 +12666,7 @@
         <v>434</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C42" s="59">
         <v>8</v>
@@ -12680,11 +12683,11 @@
         <v>1</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H42" s="16"/>
       <c r="I42" s="59" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -12692,7 +12695,7 @@
         <v>434</v>
       </c>
       <c r="B43" s="59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C43" s="59">
         <v>9</v>
@@ -12709,11 +12712,11 @@
         <v>1</v>
       </c>
       <c r="G43" s="59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="59" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12721,7 +12724,7 @@
         <v>434</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C44" s="59">
         <v>10</v>
@@ -12738,11 +12741,11 @@
         <v>1</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H44" s="16"/>
       <c r="I44" s="59" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -12750,7 +12753,7 @@
         <v>434</v>
       </c>
       <c r="B45" s="59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C45" s="59">
         <v>11</v>
@@ -12767,11 +12770,11 @@
         <v>1</v>
       </c>
       <c r="G45" s="59" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H45" s="16"/>
       <c r="I45" s="59" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12782,7 +12785,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="109" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D46" s="101">
         <v>4</v>
@@ -12796,11 +12799,11 @@
         <v>1</v>
       </c>
       <c r="G46" s="101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H46" s="66"/>
       <c r="I46" s="101" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -12811,7 +12814,7 @@
         <v>26</v>
       </c>
       <c r="C47" s="67" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D47" s="50">
         <v>16</v>
@@ -12825,11 +12828,11 @@
         <v>1</v>
       </c>
       <c r="G47" s="50" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H47" s="68"/>
       <c r="I47" s="101" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -12854,11 +12857,11 @@
         <v>1</v>
       </c>
       <c r="G48" s="51" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -12883,11 +12886,11 @@
         <v>1</v>
       </c>
       <c r="G49" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H49" s="16"/>
       <c r="I49" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -12912,11 +12915,11 @@
         <v>1</v>
       </c>
       <c r="G50" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H50" s="16"/>
       <c r="I50" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -12941,11 +12944,11 @@
         <v>1</v>
       </c>
       <c r="G51" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H51" s="16"/>
       <c r="I51" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -12953,7 +12956,7 @@
         <v>436</v>
       </c>
       <c r="B52" s="59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C52" s="59">
         <v>4</v>
@@ -12970,11 +12973,11 @@
         <v>1</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H52" s="16"/>
       <c r="I52" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -12999,11 +13002,11 @@
         <v>1</v>
       </c>
       <c r="G53" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H53" s="16"/>
       <c r="I53" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -13028,11 +13031,11 @@
         <v>1</v>
       </c>
       <c r="G54" s="59" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H54" s="16"/>
       <c r="I54" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13040,7 +13043,7 @@
         <v>436</v>
       </c>
       <c r="B55" s="59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C55" s="59">
         <v>7</v>
@@ -13057,11 +13060,11 @@
         <v>1</v>
       </c>
       <c r="G55" s="59" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H55" s="16"/>
       <c r="I55" s="59" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -13069,7 +13072,7 @@
         <v>436</v>
       </c>
       <c r="B56" s="59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C56" s="59">
         <v>8</v>
@@ -13086,11 +13089,11 @@
         <v>1</v>
       </c>
       <c r="G56" s="59" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H56" s="16"/>
       <c r="I56" s="59" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -13098,7 +13101,7 @@
         <v>436</v>
       </c>
       <c r="B57" s="59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C57" s="59">
         <v>9</v>
@@ -13115,11 +13118,11 @@
         <v>1</v>
       </c>
       <c r="G57" s="59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="59" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13127,7 +13130,7 @@
         <v>436</v>
       </c>
       <c r="B58" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C58" s="59">
         <v>10</v>
@@ -13144,11 +13147,11 @@
         <v>1</v>
       </c>
       <c r="G58" s="59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H58" s="16"/>
       <c r="I58" s="59" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -13156,7 +13159,7 @@
         <v>436</v>
       </c>
       <c r="B59" s="59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C59" s="59">
         <v>11</v>
@@ -13173,11 +13176,11 @@
         <v>1</v>
       </c>
       <c r="G59" s="59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H59" s="16"/>
       <c r="I59" s="59" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -13185,7 +13188,7 @@
         <v>436</v>
       </c>
       <c r="B60" s="59" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C60" s="59">
         <v>12</v>
@@ -13202,11 +13205,11 @@
         <v>1</v>
       </c>
       <c r="G60" s="59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="59" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -13214,7 +13217,7 @@
         <v>436</v>
       </c>
       <c r="B61" s="59" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C61" s="59">
         <v>13</v>
@@ -13231,11 +13234,11 @@
         <v>1</v>
       </c>
       <c r="G61" s="59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H61" s="16"/>
       <c r="I61" s="59" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -13243,7 +13246,7 @@
         <v>436</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C62" s="59">
         <v>14</v>
@@ -13260,11 +13263,11 @@
         <v>1</v>
       </c>
       <c r="G62" s="59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H62" s="16"/>
       <c r="I62" s="59" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13289,11 +13292,11 @@
         <v>1</v>
       </c>
       <c r="G63" s="101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H63" s="66"/>
       <c r="I63" s="101" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13318,11 +13321,11 @@
         <v>1</v>
       </c>
       <c r="G64" s="50" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H64" s="68"/>
       <c r="I64" s="50" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
@@ -13330,10 +13333,10 @@
         <v>438</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C65" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D65" s="60">
         <v>16</v>
@@ -13347,7 +13350,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H65" s="93"/>
       <c r="I65" s="60"/>
@@ -13357,10 +13360,10 @@
         <v>439</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D66" s="60">
         <v>16</v>
@@ -13374,20 +13377,20 @@
         <v>1</v>
       </c>
       <c r="G66" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H66" s="93"/>
       <c r="I66" s="60"/>
     </row>
     <row r="67" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="114" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D67" s="60">
         <v>16</v>
@@ -13401,20 +13404,20 @@
         <v>1</v>
       </c>
       <c r="G67" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H67" s="93"/>
       <c r="I67" s="60"/>
     </row>
     <row r="68" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="114" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D68" s="60">
         <v>16</v>
@@ -13428,20 +13431,20 @@
         <v>1</v>
       </c>
       <c r="G68" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H68" s="93"/>
       <c r="I68" s="60"/>
     </row>
     <row r="69" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="114" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B69" s="60" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D69" s="60">
         <v>16</v>
@@ -13455,20 +13458,20 @@
         <v>1</v>
       </c>
       <c r="G69" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H69" s="93"/>
       <c r="I69" s="60"/>
     </row>
     <row r="70" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="114" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B70" s="60" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D70" s="60">
         <v>16</v>
@@ -13482,20 +13485,20 @@
         <v>1</v>
       </c>
       <c r="G70" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H70" s="93"/>
       <c r="I70" s="60"/>
     </row>
     <row r="71" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="114" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B71" s="60" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C71" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D71" s="60">
         <v>16</v>
@@ -13509,20 +13512,20 @@
         <v>1</v>
       </c>
       <c r="G71" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H71" s="93"/>
       <c r="I71" s="60"/>
     </row>
     <row r="72" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="114" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B72" s="60" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D72" s="60">
         <v>16</v>
@@ -13536,7 +13539,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="93" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H72" s="93"/>
       <c r="I72" s="60"/>
@@ -13590,22 +13593,22 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -13616,13 +13619,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="115" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D2" s="8">
         <v>48128</v>
@@ -13636,7 +13639,7 @@
         <v>3008</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -13711,22 +13714,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -13740,10 +13743,10 @@
         <v>1000</v>
       </c>
       <c r="B2" s="111" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C2" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D2" s="111">
         <v>32</v>
@@ -13757,10 +13760,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -13769,10 +13772,10 @@
         <v>1002</v>
       </c>
       <c r="B3" s="111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D3" s="111">
         <v>32</v>
@@ -13786,10 +13789,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -13798,10 +13801,10 @@
         <v>1004</v>
       </c>
       <c r="B4" s="111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D4" s="111">
         <v>32</v>
@@ -13815,10 +13818,10 @@
         <v>2</v>
       </c>
       <c r="G4" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -13827,10 +13830,10 @@
         <v>1006</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D5" s="111">
         <v>32</v>
@@ -13844,10 +13847,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -13856,10 +13859,10 @@
         <v>1008</v>
       </c>
       <c r="B6" s="111" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D6" s="111">
         <v>32</v>
@@ -13873,10 +13876,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -13885,10 +13888,10 @@
         <v>100A</v>
       </c>
       <c r="B7" s="111" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D7" s="111">
         <v>32</v>
@@ -13902,10 +13905,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -13914,10 +13917,10 @@
         <v>100C</v>
       </c>
       <c r="B8" s="111" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D8" s="111">
         <v>32</v>
@@ -13931,10 +13934,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -13943,10 +13946,10 @@
         <v>100E</v>
       </c>
       <c r="B9" s="111" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D9" s="111">
         <v>32</v>
@@ -13960,10 +13963,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -13972,10 +13975,10 @@
         <v>1010</v>
       </c>
       <c r="B10" s="111" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C10" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" s="111">
         <v>32</v>
@@ -13989,10 +13992,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -14001,10 +14004,10 @@
         <v>1012</v>
       </c>
       <c r="B11" s="111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C11" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D11" s="111">
         <v>32</v>
@@ -14018,10 +14021,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -14030,10 +14033,10 @@
         <v>1014</v>
       </c>
       <c r="B12" s="111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C12" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D12" s="111">
         <v>32</v>
@@ -14047,10 +14050,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -14059,10 +14062,10 @@
         <v>1016</v>
       </c>
       <c r="B13" s="111" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C13" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D13" s="111">
         <v>32</v>
@@ -14076,10 +14079,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -14088,10 +14091,10 @@
         <v>1018</v>
       </c>
       <c r="B14" s="111" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C14" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D14" s="111">
         <v>32</v>
@@ -14105,10 +14108,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -14117,10 +14120,10 @@
         <v>101A</v>
       </c>
       <c r="B15" s="111" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C15" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D15" s="111">
         <v>32</v>
@@ -14134,10 +14137,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -14146,10 +14149,10 @@
         <v>101C</v>
       </c>
       <c r="B16" s="111" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C16" s="118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D16" s="111">
         <v>32</v>
@@ -14163,10 +14166,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -14175,10 +14178,10 @@
         <v>101E</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C17" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D17" s="59">
         <v>32</v>
@@ -14192,10 +14195,10 @@
         <v>2</v>
       </c>
       <c r="G17" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -14204,10 +14207,10 @@
         <v>1020</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C18" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D18" s="59">
         <v>32</v>
@@ -14221,10 +14224,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -14233,10 +14236,10 @@
         <v>1022</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C19" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D19" s="59">
         <v>32</v>
@@ -14250,10 +14253,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -14262,10 +14265,10 @@
         <v>1024</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C20" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D20" s="59">
         <v>32</v>
@@ -14279,10 +14282,10 @@
         <v>2</v>
       </c>
       <c r="G20" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -14291,10 +14294,10 @@
         <v>1026</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C21" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D21" s="59">
         <v>32</v>
@@ -14308,10 +14311,10 @@
         <v>2</v>
       </c>
       <c r="G21" s="111" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14320,10 +14323,10 @@
         <v>1028</v>
       </c>
       <c r="B22" s="101" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C22" s="97" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D22" s="101">
         <v>1920</v>
@@ -14340,7 +14343,7 @@
         <v>25</v>
       </c>
       <c r="H22" s="66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -14349,10 +14352,10 @@
         <v>10A0</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D23" s="51">
         <v>384</v>
@@ -14366,10 +14369,10 @@
         <v>24</v>
       </c>
       <c r="G23" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -14378,10 +14381,10 @@
         <v>10B8</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C24" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D24" s="59">
         <v>384</v>
@@ -14395,10 +14398,10 @@
         <v>24</v>
       </c>
       <c r="G24" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -14407,10 +14410,10 @@
         <v>10D0</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D25" s="59">
         <v>384</v>
@@ -14424,10 +14427,10 @@
         <v>24</v>
       </c>
       <c r="G25" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -14436,10 +14439,10 @@
         <v>10E8</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D26" s="59">
         <v>384</v>
@@ -14453,10 +14456,10 @@
         <v>24</v>
       </c>
       <c r="G26" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -14465,10 +14468,10 @@
         <v>1100</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D27" s="59">
         <v>384</v>
@@ -14482,10 +14485,10 @@
         <v>24</v>
       </c>
       <c r="G27" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -14494,10 +14497,10 @@
         <v>1118</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D28" s="59">
         <v>384</v>
@@ -14511,10 +14514,10 @@
         <v>24</v>
       </c>
       <c r="G28" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -14523,10 +14526,10 @@
         <v>1130</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C29" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D29" s="59">
         <v>384</v>
@@ -14540,10 +14543,10 @@
         <v>24</v>
       </c>
       <c r="G29" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -14552,10 +14555,10 @@
         <v>1148</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C30" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D30" s="59">
         <v>384</v>
@@ -14569,10 +14572,10 @@
         <v>24</v>
       </c>
       <c r="G30" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -14581,10 +14584,10 @@
         <v>1160</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D31" s="59">
         <v>384</v>
@@ -14598,10 +14601,10 @@
         <v>24</v>
       </c>
       <c r="G31" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -14610,10 +14613,10 @@
         <v>1178</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D32" s="59">
         <v>384</v>
@@ -14627,10 +14630,10 @@
         <v>24</v>
       </c>
       <c r="G32" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -14639,10 +14642,10 @@
         <v>1190</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C33" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D33" s="59">
         <v>384</v>
@@ -14656,10 +14659,10 @@
         <v>24</v>
       </c>
       <c r="G33" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -14668,10 +14671,10 @@
         <v>11A8</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C34" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D34" s="59">
         <v>384</v>
@@ -14685,10 +14688,10 @@
         <v>24</v>
       </c>
       <c r="G34" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -14697,10 +14700,10 @@
         <v>11C0</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C35" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D35" s="59">
         <v>384</v>
@@ -14714,10 +14717,10 @@
         <v>24</v>
       </c>
       <c r="G35" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -14726,10 +14729,10 @@
         <v>11D8</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C36" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D36" s="59">
         <v>384</v>
@@ -14743,10 +14746,10 @@
         <v>24</v>
       </c>
       <c r="G36" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -14755,10 +14758,10 @@
         <v>11F0</v>
       </c>
       <c r="B37" s="59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C37" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D37" s="59">
         <v>384</v>
@@ -14772,10 +14775,10 @@
         <v>24</v>
       </c>
       <c r="G37" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H37" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -14784,10 +14787,10 @@
         <v>1208</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C38" s="96" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D38" s="59">
         <v>384</v>
@@ -14801,10 +14804,10 @@
         <v>24</v>
       </c>
       <c r="G38" s="111" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H38" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -14813,10 +14816,10 @@
         <v>1220</v>
       </c>
       <c r="B39" s="59" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C39" s="96" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D39" s="59">
         <v>256</v>
@@ -14830,10 +14833,10 @@
         <v>16</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H39" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -14842,10 +14845,10 @@
         <v>1230</v>
       </c>
       <c r="B40" s="59" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D40" s="59">
         <v>256</v>
@@ -14859,10 +14862,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="59" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -14871,10 +14874,10 @@
         <v>1240</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C41" s="96" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D41" s="59">
         <v>256</v>
@@ -14888,10 +14891,10 @@
         <v>16</v>
       </c>
       <c r="G41" s="59" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H41" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -14900,10 +14903,10 @@
         <v>1250</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C42" s="96" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D42" s="59">
         <v>256</v>
@@ -14917,10 +14920,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14932,7 +14935,7 @@
         <v>25</v>
       </c>
       <c r="C43" s="96" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D43" s="59">
         <v>39424</v>
@@ -14949,7 +14952,7 @@
         <v>25</v>
       </c>
       <c r="H43" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -15000,22 +15003,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="113" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C1" s="113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D1" s="113" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="113" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="F1" s="113" t="s">
         <v>337</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>338</v>
       </c>
       <c r="G1" s="113" t="s">
         <v>18</v>
@@ -15026,10 +15029,10 @@
     </row>
     <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>303</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>304</v>
       </c>
       <c r="C2" s="16">
         <v>0</v>
@@ -15046,10 +15049,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="H2" s="18" t="s">
         <v>305</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15058,7 +15061,7 @@
         <v>1C01</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C3" s="16">
         <v>0</v>
@@ -15075,10 +15078,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="H3" s="16" t="s">
         <v>308</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15087,10 +15090,10 @@
         <v>1C02</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D4" s="16">
         <v>256</v>
@@ -15104,10 +15107,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15116,10 +15119,10 @@
         <v>1C12</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D5" s="18">
         <v>384</v>
@@ -15133,10 +15136,10 @@
         <v>24</v>
       </c>
       <c r="G5" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>313</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="158.25" x14ac:dyDescent="0.25">
@@ -15145,10 +15148,10 @@
         <v>1C2A</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D6" s="18">
         <v>768</v>
@@ -15162,10 +15165,10 @@
         <v>48</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -15174,10 +15177,10 @@
         <v>1C5A</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D7" s="18">
         <v>128</v>
@@ -15191,10 +15194,10 @@
         <v>8</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
@@ -15203,10 +15206,10 @@
         <v>1C62</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D8" s="18">
         <v>8192</v>
@@ -15220,10 +15223,10 @@
         <v>512</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -15232,10 +15235,10 @@
         <v>1E62</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D9" s="18">
         <v>768</v>
@@ -15249,10 +15252,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -15264,7 +15267,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="118" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D10" s="21">
         <v>3808</v>
@@ -15278,7 +15281,7 @@
         <v>238</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H10" s="21"/>
     </row>
@@ -15330,10 +15333,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>322</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -15344,6 +15347,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB031FF8E1109D43B2BDF0F43F684A4E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b896ebdbfa452e7a07541eac816e2062">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94916c3f-a887-466e-9071-419f2f5fc067" xmlns:ns3="0358a91d-8923-4300-9035-92feb74d70aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="556acc82b7336cf142ff4903a3ab7ecb" ns2:_="" ns3:_="">
     <xsd:import namespace="94916c3f-a887-466e-9071-419f2f5fc067"/>
@@ -15598,49 +15629,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
-    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15663,9 +15655,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
+    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
+++ b/tools/memory_map/AST2700A2_OTP_memory_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sdk\ast2700\OTP\memory\release\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\jheng-shuo_lin\socsec\tools\memory_map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215BF77B-7B06-46F4-8AFC-7FA2981CDB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467A2A65-08A1-4196-B498-038062358232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{40652B66-A45B-48BE-91E6-4A13E915CABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="734">
   <si>
     <t>High Level overview of OTP memory layout</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2862,10 +2862,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SoC FMC Hardware SVN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dis_cptra_owner_key_retry</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2889,14 +2885,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SoC FMC hardware SVN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>47: 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Disable OTP Memory Factory Test Mode
 0: enable
 1: disable
@@ -2984,10 +2972,6 @@
   <si>
     <t>The blue color fields show what would be provisioned by ASPEED.
 OTPROM, OTPCFG, OTPSTRAP, OTPCAL, OTPPUF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v2p1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3054,6 +3038,29 @@
   </si>
   <si>
     <t>800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v2p3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>175: 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retire_mechanism_option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enable key retirement mechanism option 
+0: can only retire itself key #id
+1: can retire others key #id except itself
+There are some key retire bits in OTPRBP region (ex: OTPRBP0/1/3) used of be programmed if the keys need of be retired. This option chooses the retire mechanism policy for different use cases.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4233,6 +4240,24 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4244,24 +4269,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4666,20 +4673,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="124" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="125" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -4956,19 +4963,19 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="158" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="163" t="s">
-        <v>721</v>
-      </c>
-      <c r="B18" s="164"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="164"/>
-      <c r="G18" s="165"/>
+      <c r="A18" s="169" t="s">
+        <v>718</v>
+      </c>
+      <c r="B18" s="170"/>
+      <c r="C18" s="170"/>
+      <c r="D18" s="170"/>
+      <c r="E18" s="170"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="171"/>
       <c r="L18"/>
     </row>
   </sheetData>
@@ -5444,11 +5451,11 @@
         <v>16</v>
       </c>
       <c r="E2" s="8">
-        <f t="shared" ref="E2:E12" si="0">QUOTIENT(D2+7,8)</f>
+        <f t="shared" ref="E2:E3" si="0">QUOTIENT(D2+7,8)</f>
         <v>2</v>
       </c>
       <c r="F2" s="8">
-        <f t="shared" ref="F2:F12" si="1">QUOTIENT(E2+1,2)</f>
+        <f t="shared" ref="F2:F3" si="1">QUOTIENT(E2+1,2)</f>
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
@@ -5458,7 +5465,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="145" t="str">
-        <f t="shared" ref="A3:A13" si="2">DEC2HEX(HEX2DEC(A2)+F2)</f>
+        <f t="shared" ref="A3:A8" si="2">DEC2HEX(HEX2DEC(A2)+F2)</f>
         <v>3E1</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -5533,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>27</v>
@@ -5562,7 +5569,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>29</v>
@@ -5628,7 +5635,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="145" t="str">
-        <f t="shared" ref="A9:A12" si="5">DEC2HEX(HEX2DEC(A8)+F8)</f>
+        <f>DEC2HEX(HEX2DEC(A8)+F8)</f>
         <v>3F2</v>
       </c>
       <c r="B9" s="18" t="s">
@@ -5641,11 +5648,11 @@
         <v>4</v>
       </c>
       <c r="E9" s="18">
-        <f t="shared" ref="E9:E11" si="6">QUOTIENT(D9+7,8)</f>
+        <f t="shared" ref="E9:E12" si="5">QUOTIENT(D9+7,8)</f>
         <v>1</v>
       </c>
       <c r="F9" s="18">
-        <f t="shared" ref="F9:F11" si="7">QUOTIENT(E9+1,2)</f>
+        <f t="shared" ref="F9:F12" si="6">QUOTIENT(E9+1,2)</f>
         <v>1</v>
       </c>
       <c r="G9" s="21" t="s">
@@ -5657,94 +5664,90 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="145" t="str">
+        <f>DEC2HEX(HEX2DEC(A9)+F9)</f>
+        <v>3F3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>731</v>
+      </c>
+      <c r="D10" s="16">
+        <v>12</v>
+      </c>
+      <c r="E10" s="18">
         <f t="shared" si="5"/>
-        <v>3F3</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>322</v>
-      </c>
-      <c r="D10" s="16">
-        <v>32</v>
-      </c>
-      <c r="E10" s="18">
+        <v>2</v>
+      </c>
+      <c r="F10" s="18">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F10" s="18">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>36</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="145" t="str">
+        <f>DEC2HEX(HEX2DEC(A9)+F9)</f>
+        <v>3F3</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>322</v>
+      </c>
+      <c r="D11" s="16">
+        <v>32</v>
+      </c>
+      <c r="E11" s="18">
         <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="145" t="str">
+        <f t="shared" ref="A12" si="7">DEC2HEX(HEX2DEC(A11)+F11)</f>
         <v>3F5</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>694</v>
-      </c>
-      <c r="C11" s="95" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" s="16">
-        <v>128</v>
-      </c>
-      <c r="E11" s="18">
+      <c r="B12" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>730</v>
+      </c>
+      <c r="D12" s="16">
+        <v>176</v>
+      </c>
+      <c r="E12" s="18">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="F12" s="18">
         <f t="shared" si="6"/>
-        <v>16</v>
-      </c>
-      <c r="F11" s="18">
-        <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="148" t="str">
-        <f t="shared" si="5"/>
-        <v>3FD</v>
-      </c>
-      <c r="B12" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="62" t="s">
-        <v>700</v>
-      </c>
-      <c r="D12" s="24">
-        <v>48</v>
-      </c>
-      <c r="E12" s="24">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="F12" s="24">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f>DEC2HEX(HEX2DEC(A12)+F12)</f>
         <v>400</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -5753,14 +5756,14 @@
       <c r="C13" s="60"/>
       <c r="D13" s="12">
         <f>SUM(D2:D12)</f>
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="E13" s="12">
-        <f>SUM(E2:E12)</f>
-        <v>63</v>
+        <f>QUOTIENT(D13+7,8)</f>
+        <v>64</v>
       </c>
       <c r="F13" s="12">
-        <f>SUM(F2:F12)</f>
+        <f>QUOTIENT(E13+1,2)</f>
         <v>32</v>
       </c>
       <c r="G13" s="12"/>
@@ -5776,7 +5779,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8">
-        <f>F13*16</f>
+        <f>D13</f>
         <v>512</v>
       </c>
       <c r="E14" s="8">
@@ -5926,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>370</v>
@@ -6059,12 +6062,12 @@
         <v>334</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A9" s="119">
         <v>400</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>25</v>
+        <v>732</v>
       </c>
       <c r="C9" s="63">
         <v>8</v>
@@ -6081,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="71" t="s">
-        <v>25</v>
+        <v>733</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>370</v>
@@ -6405,7 +6408,7 @@
         <v>402</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C20" s="63">
         <v>14</v>
@@ -6422,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H20" s="34"/>
       <c r="I20" s="19" t="s">
@@ -6567,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="78" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="H25" s="58" t="s">
         <v>402</v>
@@ -7960,7 +7963,7 @@
         <v>344</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C71" s="99">
         <v>7</v>
@@ -7977,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H71" s="58" t="s">
         <v>408</v>
@@ -7991,7 +7994,7 @@
         <v>344</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C72" s="99">
         <v>6</v>
@@ -8008,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="85" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H72" s="58" t="s">
         <v>408</v>
@@ -8022,7 +8025,7 @@
         <v>344</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C73" s="99">
         <v>5</v>
@@ -8039,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="89" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="H73" s="58" t="s">
         <v>408</v>
@@ -8053,7 +8056,7 @@
         <v>344</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C74" s="99">
         <v>4</v>
@@ -8070,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="89" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="H74" s="58" t="s">
         <v>408</v>
@@ -8084,7 +8087,7 @@
         <v>344</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C75" s="99">
         <v>3</v>
@@ -8101,7 +8104,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="89" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H75" s="58" t="s">
         <v>408</v>
@@ -8115,7 +8118,7 @@
         <v>344</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C76" s="99">
         <v>2</v>
@@ -8132,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="89" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H76" s="58" t="s">
         <v>408</v>
@@ -8145,8 +8148,8 @@
       <c r="A77" s="119" t="s">
         <v>344</v>
       </c>
-      <c r="B77" s="171" t="s">
-        <v>706</v>
+      <c r="B77" s="167" t="s">
+        <v>703</v>
       </c>
       <c r="C77" s="63">
         <v>1</v>
@@ -8177,7 +8180,7 @@
         <v>344</v>
       </c>
       <c r="B78" s="81" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C78" s="94">
         <v>0</v>
@@ -10415,7 +10418,7 @@
         <v>548</v>
       </c>
       <c r="H2" s="161" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="I2" s="143"/>
     </row>
@@ -10444,7 +10447,7 @@
         <v>549</v>
       </c>
       <c r="H3" s="161" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I3" s="143"/>
     </row>
@@ -11022,7 +11025,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>195</v>
@@ -12253,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>642</v>
@@ -13906,14 +13909,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="163" t="s">
         <v>565</v>
       </c>
-      <c r="B2" s="168" t="s">
-        <v>726</v>
-      </c>
-      <c r="C2" s="169" t="s">
-        <v>729</v>
+      <c r="B2" s="164" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2" s="165" t="s">
+        <v>725</v>
       </c>
       <c r="D2" s="67">
         <v>5120</v>
@@ -13926,20 +13929,20 @@
         <f t="shared" ref="F2" si="1">QUOTIENT(E2+1,2)</f>
         <v>320</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="166" t="s">
         <v>652</v>
       </c>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="167" t="s">
-        <v>730</v>
-      </c>
-      <c r="B3" s="168" t="s">
-        <v>727</v>
-      </c>
-      <c r="C3" s="169" t="s">
-        <v>729</v>
+      <c r="A3" s="163" t="s">
+        <v>726</v>
+      </c>
+      <c r="B3" s="164" t="s">
+        <v>723</v>
+      </c>
+      <c r="C3" s="165" t="s">
+        <v>725</v>
       </c>
       <c r="D3" s="67">
         <v>5120</v>
@@ -13952,20 +13955,20 @@
         <f t="shared" ref="F3:F4" si="3">QUOTIENT(E3+1,2)</f>
         <v>320</v>
       </c>
-      <c r="G3" s="170" t="s">
+      <c r="G3" s="166" t="s">
         <v>652</v>
       </c>
       <c r="H3" s="156"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="167" t="s">
-        <v>731</v>
-      </c>
-      <c r="B4" s="168" t="s">
-        <v>728</v>
-      </c>
-      <c r="C4" s="169" t="s">
-        <v>729</v>
+      <c r="A4" s="163" t="s">
+        <v>727</v>
+      </c>
+      <c r="B4" s="164" t="s">
+        <v>724</v>
+      </c>
+      <c r="C4" s="165" t="s">
+        <v>725</v>
       </c>
       <c r="D4" s="67">
         <v>5120</v>
@@ -13978,20 +13981,20 @@
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
-      <c r="G4" s="170" t="s">
+      <c r="G4" s="166" t="s">
         <v>652</v>
       </c>
       <c r="H4" s="156"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="155" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B5" s="157" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D5" s="8">
         <v>32768</v>
@@ -14004,8 +14007,8 @@
         <f t="shared" ref="F5" si="5">QUOTIENT(E5+1,2)</f>
         <v>2048</v>
       </c>
-      <c r="G5" s="166" t="s">
-        <v>704</v>
+      <c r="G5" s="162" t="s">
+        <v>701</v>
       </c>
       <c r="H5" s="156"/>
     </row>
@@ -15713,34 +15716,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FB031FF8E1109D43B2BDF0F43F684A4E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b896ebdbfa452e7a07541eac816e2062">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94916c3f-a887-466e-9071-419f2f5fc067" xmlns:ns3="0358a91d-8923-4300-9035-92feb74d70aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="556acc82b7336cf142ff4903a3ab7ecb" ns2:_="" ns3:_="">
     <xsd:import namespace="94916c3f-a887-466e-9071-419f2f5fc067"/>
@@ -15995,10 +15970,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0358a91d-8923-4300-9035-92feb74d70aa">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="94916c3f-a887-466e-9071-419f2f5fc067" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0358a91d-8923-4300-9035-92feb74d70aa" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94916c3f-a887-466e-9071-419f2f5fc067">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
+    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16021,20 +16035,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15AAF0E9-722A-46AD-84E0-1D9BE67AFFE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06808489-AD29-49EF-A920-5725306266D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="94916c3f-a887-466e-9071-419f2f5fc067"/>
-    <ds:schemaRef ds:uri="0358a91d-8923-4300-9035-92feb74d70aa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>